--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -3986,10 +3986,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118655215</v>
+        <v>118649845</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3998,55 +3998,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471154</v>
+        <v>471124</v>
       </c>
       <c r="R29" t="n">
-        <v>7140912</v>
+        <v>7140767</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4070,12 +4056,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4102,10 +4098,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118649845</v>
+        <v>118658352</v>
       </c>
       <c r="B30" t="n">
-        <v>90522</v>
+        <v>56494</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4118,37 +4114,52 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471124</v>
+        <v>471000</v>
       </c>
       <c r="R30" t="n">
-        <v>7140767</v>
+        <v>7140830</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4172,22 +4183,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4214,10 +4225,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118658352</v>
+        <v>118655215</v>
       </c>
       <c r="B31" t="n">
-        <v>56494</v>
+        <v>97846</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4226,41 +4237,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4269,10 +4279,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471000</v>
+        <v>471154</v>
       </c>
       <c r="R31" t="n">
-        <v>7140830</v>
+        <v>7140912</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4302,19 +4312,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:08</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1168,7 +1168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118610418</v>
+        <v>118611103</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471080</v>
+        <v>470955</v>
       </c>
       <c r="R6" t="n">
-        <v>7140963</v>
+        <v>7140903</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1268,11 +1268,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1289,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118619895</v>
+        <v>118610418</v>
       </c>
       <c r="B7" t="n">
-        <v>56494</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,56 +1296,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot (Håkafot), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>471080</v>
       </c>
       <c r="R7" t="n">
-        <v>7140901</v>
+        <v>7140963</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1377,19 +1371,9 @@
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118610957</v>
+        <v>118619895</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>56494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,40 +1417,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1475,13 +1460,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471000</v>
+        <v>471080</v>
       </c>
       <c r="R8" t="n">
-        <v>7140801</v>
+        <v>7140901</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1508,11 +1493,21 @@
           <t>2024-07-22</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-22</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1521,6 +1516,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1537,7 +1537,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118610565</v>
+        <v>118610548</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1637,6 +1637,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1653,7 +1658,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118609933</v>
+        <v>118610096</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1688,17 +1693,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1774,7 +1774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118613050</v>
+        <v>118613059</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1890,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118611120</v>
+        <v>118615387</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1902,52 +1902,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470955</v>
+        <v>471126</v>
       </c>
       <c r="R12" t="n">
-        <v>7140903</v>
+        <v>7140737</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1990,6 +1976,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2006,7 +2007,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118608782</v>
+        <v>118610965</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -2046,7 +2047,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2056,14 +2057,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Håagkat (Håagkat), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471181</v>
+        <v>471000</v>
       </c>
       <c r="R13" t="n">
-        <v>7140954</v>
+        <v>7140801</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2122,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118615387</v>
+        <v>118610117</v>
       </c>
       <c r="B14" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2134,38 +2135,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat (Håagkat), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471126</v>
+        <v>471181</v>
       </c>
       <c r="R14" t="n">
-        <v>7140737</v>
+        <v>7140954</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2209,19 +2224,9 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2239,7 +2244,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118643112</v>
+        <v>118633149</v>
       </c>
       <c r="B15" t="n">
         <v>56494</v>
@@ -2274,17 +2279,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äggskal</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471124</v>
+        <v>471126</v>
       </c>
       <c r="R15" t="n">
-        <v>7140767</v>
+        <v>7140737</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2328,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2338,7 +2343,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,7 +2370,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118633149</v>
+        <v>118632946</v>
       </c>
       <c r="B16" t="n">
         <v>56494</v>
@@ -2400,17 +2405,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2419,10 +2424,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471126</v>
+        <v>471124</v>
       </c>
       <c r="R16" t="n">
-        <v>7140737</v>
+        <v>7140767</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2465,6 +2470,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2491,10 +2501,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118654541</v>
+        <v>118656413</v>
       </c>
       <c r="B17" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2503,40 +2513,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2545,13 +2555,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471220</v>
+        <v>471159</v>
       </c>
       <c r="R17" t="n">
-        <v>7140873</v>
+        <v>7140899</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2575,22 +2585,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minat 45 bladrosetter över ca 1 kvm yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2617,10 +2632,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118658808</v>
+        <v>118656647</v>
       </c>
       <c r="B18" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2629,40 +2644,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2671,13 +2681,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471124</v>
+        <v>471105</v>
       </c>
       <c r="R18" t="n">
-        <v>7140767</v>
+        <v>7140950</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2706,7 +2716,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2716,7 +2726,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Va. 4 kvm med bladrosetter. Stor del mattbildande.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2743,7 +2758,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118656413</v>
+        <v>118655215</v>
       </c>
       <c r="B19" t="n">
         <v>97846</v>
@@ -2778,17 +2793,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2797,10 +2812,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471159</v>
+        <v>471154</v>
       </c>
       <c r="R19" t="n">
-        <v>7140899</v>
+        <v>7140912</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2830,24 +2845,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minat 45 bladrosetter över ca 1 kvm yta.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2874,10 +2874,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118655326</v>
+        <v>118649845</v>
       </c>
       <c r="B20" t="n">
-        <v>57401</v>
+        <v>90522</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,55 +2886,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471150</v>
+        <v>471124</v>
       </c>
       <c r="R20" t="n">
-        <v>7140890</v>
+        <v>7140767</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2958,22 +2944,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3000,7 +2986,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118656215</v>
+        <v>118656261</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -3035,7 +3021,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3126,10 +3112,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118652356</v>
+        <v>118657575</v>
       </c>
       <c r="B22" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3138,31 +3124,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3171,13 +3166,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471011</v>
+        <v>470892</v>
       </c>
       <c r="R22" t="n">
-        <v>7140906</v>
+        <v>7140851</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3201,22 +3196,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3243,7 +3238,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118654317</v>
+        <v>118652356</v>
       </c>
       <c r="B23" t="n">
         <v>57306</v>
@@ -3284,14 +3279,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471203</v>
+        <v>471011</v>
       </c>
       <c r="R23" t="n">
-        <v>7140769</v>
+        <v>7140906</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3323,7 +3318,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3333,12 +3328,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosök Spillkråka</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3365,10 +3355,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118657575</v>
+        <v>118653001</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>56494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3377,40 +3367,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3419,13 +3409,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470892</v>
+        <v>471105</v>
       </c>
       <c r="R24" t="n">
-        <v>7140851</v>
+        <v>7140803</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3449,22 +3439,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3491,7 +3481,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118656647</v>
+        <v>118655082</v>
       </c>
       <c r="B25" t="n">
         <v>97846</v>
@@ -3526,7 +3516,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3534,19 +3524,24 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471105</v>
+        <v>471177</v>
       </c>
       <c r="R25" t="n">
-        <v>7140950</v>
+        <v>7140901</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3573,24 +3568,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Va. 4 kvm med bladrosetter. Stor del mattbildande.</t>
+          <t>Över ca. 20 kvm ytan rosetter och stänglar i blom i olika fält. Även spridda rosetter i mossan.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3617,10 +3602,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118653001</v>
+        <v>118649741</v>
       </c>
       <c r="B26" t="n">
-        <v>56494</v>
+        <v>90515</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3629,55 +3614,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>1205</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471105</v>
+        <v>471038</v>
       </c>
       <c r="R26" t="n">
-        <v>7140803</v>
+        <v>7140797</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3706,7 +3677,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3716,7 +3687,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3743,10 +3714,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118653585</v>
+        <v>118656092</v>
       </c>
       <c r="B27" t="n">
-        <v>79600</v>
+        <v>57306</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3755,41 +3726,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471126</v>
+        <v>471143</v>
       </c>
       <c r="R27" t="n">
-        <v>7140737</v>
+        <v>7141012</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3813,22 +3789,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3855,10 +3831,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118658516</v>
+        <v>118655326</v>
       </c>
       <c r="B28" t="n">
-        <v>97846</v>
+        <v>57401</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3867,40 +3843,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3909,13 +3885,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471011</v>
+        <v>471150</v>
       </c>
       <c r="R28" t="n">
-        <v>7140807</v>
+        <v>7140890</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3944,7 +3920,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3954,12 +3930,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3986,10 +3957,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118649845</v>
+        <v>118654541</v>
       </c>
       <c r="B29" t="n">
-        <v>90522</v>
+        <v>97763</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3998,41 +3969,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471124</v>
+        <v>471220</v>
       </c>
       <c r="R29" t="n">
-        <v>7140767</v>
+        <v>7140873</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4061,7 +4046,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4071,7 +4056,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4098,7 +4083,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118658352</v>
+        <v>118655469</v>
       </c>
       <c r="B30" t="n">
         <v>56494</v>
@@ -4131,20 +4116,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>äggskal</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4153,13 +4137,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471000</v>
+        <v>471147</v>
       </c>
       <c r="R30" t="n">
-        <v>7140830</v>
+        <v>7140935</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4188,7 +4172,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4198,7 +4182,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4225,10 +4214,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118655215</v>
+        <v>118658352</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>56494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4237,40 +4226,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4279,10 +4269,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471154</v>
+        <v>471000</v>
       </c>
       <c r="R31" t="n">
-        <v>7140912</v>
+        <v>7140830</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4312,9 +4302,19 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4341,10 +4341,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118655082</v>
+        <v>118653585</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>79600</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4353,52 +4353,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471177</v>
+        <v>471126</v>
       </c>
       <c r="R32" t="n">
-        <v>7140901</v>
+        <v>7140737</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4425,17 +4411,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Över ca. 20 kvm ytan rosetter och stänglar i blom i olika fält. Även spridda rosetter i mossan.</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4462,10 +4453,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118649741</v>
+        <v>118652300</v>
       </c>
       <c r="B33" t="n">
-        <v>90515</v>
+        <v>57306</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4474,41 +4465,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471038</v>
+        <v>470932</v>
       </c>
       <c r="R33" t="n">
-        <v>7140797</v>
+        <v>7140929</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4537,7 +4533,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4547,7 +4543,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4574,10 +4570,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118656092</v>
+        <v>118657198</v>
       </c>
       <c r="B34" t="n">
-        <v>57306</v>
+        <v>56494</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4590,16 +4586,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4608,9 +4604,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4619,10 +4625,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471143</v>
+        <v>470996</v>
       </c>
       <c r="R34" t="n">
-        <v>7141012</v>
+        <v>7140928</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4654,7 +4660,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4664,7 +4670,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Järpe med ungar boplats vid vindfällen</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4691,10 +4702,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118652300</v>
+        <v>118658516</v>
       </c>
       <c r="B35" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4703,31 +4714,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4736,10 +4756,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>470932</v>
+        <v>471011</v>
       </c>
       <c r="R35" t="n">
-        <v>7140929</v>
+        <v>7140807</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4766,22 +4786,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4808,10 +4833,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118655469</v>
+        <v>118658808</v>
       </c>
       <c r="B36" t="n">
-        <v>56494</v>
+        <v>97763</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4820,25 +4845,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4846,14 +4871,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>ägg</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äggskal</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4862,13 +4887,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471147</v>
+        <v>471124</v>
       </c>
       <c r="R36" t="n">
-        <v>7140935</v>
+        <v>7140767</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4897,7 +4922,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4907,12 +4932,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4939,10 +4959,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118657198</v>
+        <v>118654317</v>
       </c>
       <c r="B37" t="n">
-        <v>56494</v>
+        <v>57306</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4955,16 +4975,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4973,34 +4993,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>470996</v>
+        <v>471203</v>
       </c>
       <c r="R37" t="n">
-        <v>7140928</v>
+        <v>7140769</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5024,7 +5034,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -5034,7 +5044,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5044,7 +5054,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Järpe med ungar boplats vid vindfällen</t>
+          <t>Födosök Spillkråka</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -3714,10 +3714,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118656092</v>
+        <v>118655326</v>
       </c>
       <c r="B27" t="n">
-        <v>57306</v>
+        <v>57401</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3726,20 +3726,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3747,7 +3747,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3759,13 +3768,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471143</v>
+        <v>471150</v>
       </c>
       <c r="R27" t="n">
-        <v>7141012</v>
+        <v>7140890</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3794,7 +3803,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3804,7 +3813,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3831,10 +3840,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118655326</v>
+        <v>118656092</v>
       </c>
       <c r="B28" t="n">
-        <v>57401</v>
+        <v>57306</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3843,20 +3852,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3864,16 +3873,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471150</v>
+        <v>471143</v>
       </c>
       <c r="R28" t="n">
-        <v>7140890</v>
+        <v>7141012</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1168,7 +1168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118611103</v>
+        <v>118608782</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1203,29 +1203,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håagkat (Håagkat), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470955</v>
+        <v>471181</v>
       </c>
       <c r="R6" t="n">
-        <v>7140903</v>
+        <v>7140954</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118610418</v>
+        <v>118613059</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1329,19 +1329,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471080</v>
+        <v>471123</v>
       </c>
       <c r="R7" t="n">
-        <v>7140963</v>
+        <v>7140909</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1384,11 +1384,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118619895</v>
+        <v>118610957</v>
       </c>
       <c r="B8" t="n">
-        <v>56494</v>
+        <v>97846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,41 +1412,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1460,13 +1454,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471080</v>
+        <v>471000</v>
       </c>
       <c r="R8" t="n">
-        <v>7140901</v>
+        <v>7140801</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1493,21 +1487,11 @@
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1516,11 +1500,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1537,7 +1516,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118610548</v>
+        <v>118610096</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1572,7 +1551,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1580,21 +1559,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håagkat (Håagkat), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471004</v>
+        <v>471229</v>
       </c>
       <c r="R9" t="n">
-        <v>7140974</v>
+        <v>7140929</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1658,7 +1632,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118610096</v>
+        <v>118610565</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1693,7 +1667,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1701,16 +1675,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håagkat (Håagkat), Jmt</t>
+          <t>Håkafot (Håkafot), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471229</v>
+        <v>471004</v>
       </c>
       <c r="R10" t="n">
-        <v>7140929</v>
+        <v>7140974</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1753,11 +1732,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1774,7 +1748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118613059</v>
+        <v>118610418</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1809,7 +1783,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1819,19 +1793,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot (Håkafot), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471123</v>
+        <v>471080</v>
       </c>
       <c r="R11" t="n">
-        <v>7140909</v>
+        <v>7140963</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1874,6 +1848,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1890,10 +1869,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118615387</v>
+        <v>118611120</v>
       </c>
       <c r="B12" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1902,38 +1881,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot (Håkafot), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471126</v>
+        <v>470955</v>
       </c>
       <c r="R12" t="n">
-        <v>7140737</v>
+        <v>7140903</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1976,21 +1969,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2007,10 +1985,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118610965</v>
+        <v>118619895</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>56494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,40 +1997,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2061,13 +2040,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471000</v>
+        <v>471080</v>
       </c>
       <c r="R13" t="n">
-        <v>7140801</v>
+        <v>7140901</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,11 +2073,21 @@
           <t>2024-07-22</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-22</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2107,6 +2096,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2123,10 +2117,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118610117</v>
+        <v>118615387</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,52 +2129,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Håagkat (Håagkat), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471181</v>
+        <v>471126</v>
       </c>
       <c r="R14" t="n">
-        <v>7140954</v>
+        <v>7140737</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2224,9 +2204,19 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2370,7 +2360,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118632946</v>
+        <v>118643112</v>
       </c>
       <c r="B16" t="n">
         <v>56494</v>
@@ -2415,7 +2405,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äggskal</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2459,7 +2449,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,12 +2459,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2501,10 +2486,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118656413</v>
+        <v>118654541</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,40 +2498,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2555,13 +2540,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471159</v>
+        <v>471220</v>
       </c>
       <c r="R17" t="n">
-        <v>7140899</v>
+        <v>7140873</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2585,27 +2570,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minat 45 bladrosetter över ca 1 kvm yta.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2632,10 +2612,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118656647</v>
+        <v>118653001</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>56494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2644,35 +2624,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2684,7 +2669,7 @@
         <v>471105</v>
       </c>
       <c r="R18" t="n">
-        <v>7140950</v>
+        <v>7140803</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2711,27 +2696,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Va. 4 kvm med bladrosetter. Stor del mattbildande.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2758,7 +2738,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118655215</v>
+        <v>118656261</v>
       </c>
       <c r="B19" t="n">
         <v>97846</v>
@@ -2793,12 +2773,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2812,13 +2792,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471154</v>
+        <v>471176</v>
       </c>
       <c r="R19" t="n">
-        <v>7140912</v>
+        <v>7140877</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2845,9 +2825,19 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2874,10 +2864,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118649845</v>
+        <v>118656527</v>
       </c>
       <c r="B20" t="n">
-        <v>90522</v>
+        <v>97846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,41 +2876,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471124</v>
+        <v>471159</v>
       </c>
       <c r="R20" t="n">
-        <v>7140767</v>
+        <v>7140899</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2944,22 +2948,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2986,7 +2990,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118656261</v>
+        <v>118654949</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -3021,7 +3025,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3040,13 +3044,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471176</v>
+        <v>471177</v>
       </c>
       <c r="R21" t="n">
-        <v>7140877</v>
+        <v>7140901</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3073,19 +3077,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3112,7 +3106,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118657575</v>
+        <v>118656647</v>
       </c>
       <c r="B22" t="n">
         <v>97846</v>
@@ -3152,12 +3146,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3166,13 +3155,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470892</v>
+        <v>471105</v>
       </c>
       <c r="R22" t="n">
-        <v>7140851</v>
+        <v>7140950</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3201,7 +3190,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3211,7 +3200,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Va. 4 kvm med bladrosetter. Stor del mattbildande.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3238,10 +3232,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118652356</v>
+        <v>118655326</v>
       </c>
       <c r="B23" t="n">
-        <v>57306</v>
+        <v>57401</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3250,20 +3244,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3271,7 +3265,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3283,13 +3286,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471011</v>
+        <v>471150</v>
       </c>
       <c r="R23" t="n">
-        <v>7140906</v>
+        <v>7140890</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3313,22 +3316,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3355,10 +3358,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118653001</v>
+        <v>118652300</v>
       </c>
       <c r="B24" t="n">
-        <v>56494</v>
+        <v>57306</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3371,16 +3374,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3388,19 +3391,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3409,10 +3403,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471105</v>
+        <v>470932</v>
       </c>
       <c r="R24" t="n">
-        <v>7140803</v>
+        <v>7140929</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3444,7 +3438,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3454,7 +3448,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3481,10 +3475,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118655082</v>
+        <v>118658352</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>56494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3493,40 +3487,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3535,13 +3530,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471177</v>
+        <v>471000</v>
       </c>
       <c r="R25" t="n">
-        <v>7140901</v>
+        <v>7140830</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3568,14 +3563,19 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Över ca. 20 kvm ytan rosetter och stänglar i blom i olika fält. Även spridda rosetter i mossan.</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3602,10 +3602,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118649741</v>
+        <v>118654317</v>
       </c>
       <c r="B26" t="n">
-        <v>90515</v>
+        <v>57306</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3614,41 +3614,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471038</v>
+        <v>471203</v>
       </c>
       <c r="R26" t="n">
-        <v>7140797</v>
+        <v>7140769</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3677,7 +3682,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3687,7 +3692,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosök Spillkråka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3714,10 +3724,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118655326</v>
+        <v>118655282</v>
       </c>
       <c r="B27" t="n">
-        <v>57401</v>
+        <v>97846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3726,40 +3736,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3768,13 +3778,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471150</v>
+        <v>471154</v>
       </c>
       <c r="R27" t="n">
-        <v>7140890</v>
+        <v>7140912</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3801,19 +3811,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3840,10 +3840,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118656092</v>
+        <v>118649845</v>
       </c>
       <c r="B28" t="n">
-        <v>57306</v>
+        <v>90522</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3856,42 +3856,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471143</v>
+        <v>471124</v>
       </c>
       <c r="R28" t="n">
-        <v>7141012</v>
+        <v>7140767</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3915,22 +3910,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3957,10 +3952,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118654541</v>
+        <v>118656092</v>
       </c>
       <c r="B29" t="n">
-        <v>97763</v>
+        <v>57306</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3969,40 +3964,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4011,13 +3997,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471220</v>
+        <v>471143</v>
       </c>
       <c r="R29" t="n">
-        <v>7140873</v>
+        <v>7141012</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4041,22 +4027,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4214,10 +4200,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118658352</v>
+        <v>118649741</v>
       </c>
       <c r="B31" t="n">
-        <v>56494</v>
+        <v>90515</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4226,56 +4212,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>1205</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471000</v>
+        <v>471038</v>
       </c>
       <c r="R31" t="n">
-        <v>7140830</v>
+        <v>7140797</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4299,22 +4270,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4453,10 +4424,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118652300</v>
+        <v>118658808</v>
       </c>
       <c r="B33" t="n">
-        <v>57306</v>
+        <v>97763</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4465,31 +4436,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4498,13 +4478,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470932</v>
+        <v>471124</v>
       </c>
       <c r="R33" t="n">
-        <v>7140929</v>
+        <v>7140767</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4528,22 +4508,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4570,10 +4550,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118657198</v>
+        <v>118657609</v>
       </c>
       <c r="B34" t="n">
-        <v>56494</v>
+        <v>97846</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4582,41 +4562,40 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4625,13 +4604,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470996</v>
+        <v>470892</v>
       </c>
       <c r="R34" t="n">
-        <v>7140928</v>
+        <v>7140851</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4660,7 +4639,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4670,12 +4649,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Järpe med ungar boplats vid vindfällen</t>
+          <t>Minst 14 plantor/rosetter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4702,10 +4681,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118658516</v>
+        <v>118657198</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>56494</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4714,40 +4693,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4756,10 +4736,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471011</v>
+        <v>470996</v>
       </c>
       <c r="R35" t="n">
-        <v>7140807</v>
+        <v>7140928</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4791,7 +4771,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4801,12 +4781,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
+          <t>Järpe med ungar boplats vid vindfällen</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4833,10 +4813,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118658808</v>
+        <v>118652356</v>
       </c>
       <c r="B36" t="n">
-        <v>97763</v>
+        <v>57306</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4845,40 +4825,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4887,13 +4858,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471124</v>
+        <v>471011</v>
       </c>
       <c r="R36" t="n">
-        <v>7140767</v>
+        <v>7140906</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4917,22 +4888,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4959,10 +4930,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118654317</v>
+        <v>118658516</v>
       </c>
       <c r="B37" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4971,46 +4942,55 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471203</v>
+        <v>471011</v>
       </c>
       <c r="R37" t="n">
-        <v>7140769</v>
+        <v>7140807</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5034,27 +5014,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Födosök Spillkråka</t>
+          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118608782</v>
+        <v>118610565</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1218,14 +1218,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Håagkat (Håagkat), Jmt</t>
+          <t>Håkafot (Håkafot), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471181</v>
+        <v>471004</v>
       </c>
       <c r="R6" t="n">
-        <v>7140954</v>
+        <v>7140974</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1287,7 +1287,7 @@
         <v>118613059</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118610957</v>
+        <v>118609933</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1450,14 +1450,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat (Håagkat), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471000</v>
+        <v>471229</v>
       </c>
       <c r="R8" t="n">
-        <v>7140801</v>
+        <v>7140929</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1500,6 +1500,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118610096</v>
+        <v>118615387</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,47 +1533,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håagkat (Håagkat), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471229</v>
+        <v>471126</v>
       </c>
       <c r="R9" t="n">
-        <v>7140929</v>
+        <v>7140737</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1612,9 +1608,19 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118610565</v>
+        <v>118619895</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>56494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,55 +1650,56 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471004</v>
+        <v>471080</v>
       </c>
       <c r="R10" t="n">
-        <v>7140974</v>
+        <v>7140901</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1719,11 +1726,21 @@
           <t>2024-07-22</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-22</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1732,6 +1749,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1748,10 +1770,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118610418</v>
+        <v>118610117</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1783,7 +1805,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1798,14 +1820,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håagkat (Håagkat), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471080</v>
+        <v>471181</v>
       </c>
       <c r="R11" t="n">
-        <v>7140963</v>
+        <v>7140954</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1872,7 +1894,7 @@
         <v>118611120</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,10 +2007,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118619895</v>
+        <v>118610965</v>
       </c>
       <c r="B13" t="n">
-        <v>56494</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,41 +2019,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2040,13 +2061,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471080</v>
+        <v>471000</v>
       </c>
       <c r="R13" t="n">
-        <v>7140901</v>
+        <v>7140801</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2073,21 +2094,11 @@
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2096,11 +2107,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2117,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118615387</v>
+        <v>118610418</v>
       </c>
       <c r="B14" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2129,38 +2135,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot (Håkafot), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471126</v>
+        <v>471080</v>
       </c>
       <c r="R14" t="n">
-        <v>7140737</v>
+        <v>7140963</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2204,19 +2224,9 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2234,7 +2244,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118633149</v>
+        <v>118643112</v>
       </c>
       <c r="B15" t="n">
         <v>56494</v>
@@ -2269,17 +2279,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>äggskal</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2288,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471126</v>
+        <v>471124</v>
       </c>
       <c r="R15" t="n">
-        <v>7140737</v>
+        <v>7140767</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2323,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2333,7 +2343,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2360,7 +2370,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118643112</v>
+        <v>118633149</v>
       </c>
       <c r="B16" t="n">
         <v>56494</v>
@@ -2395,17 +2405,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äggskal</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2414,10 +2424,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471124</v>
+        <v>471126</v>
       </c>
       <c r="R16" t="n">
-        <v>7140767</v>
+        <v>7140737</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2449,7 +2459,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2459,7 +2469,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2486,10 +2496,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118654541</v>
+        <v>118652356</v>
       </c>
       <c r="B17" t="n">
-        <v>97763</v>
+        <v>57306</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2498,40 +2508,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2540,13 +2541,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471220</v>
+        <v>471011</v>
       </c>
       <c r="R17" t="n">
-        <v>7140873</v>
+        <v>7140906</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2575,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2585,7 +2586,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2612,10 +2613,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118653001</v>
+        <v>118656215</v>
       </c>
       <c r="B18" t="n">
-        <v>56494</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2624,40 +2625,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2666,10 +2667,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471105</v>
+        <v>471176</v>
       </c>
       <c r="R18" t="n">
-        <v>7140803</v>
+        <v>7140877</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2696,22 +2697,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2738,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118656261</v>
+        <v>118653585</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>79607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2750,55 +2751,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471176</v>
+        <v>471126</v>
       </c>
       <c r="R19" t="n">
-        <v>7140877</v>
+        <v>7140737</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2822,22 +2809,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2864,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118656527</v>
+        <v>118658516</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2899,17 +2886,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2918,13 +2905,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471159</v>
+        <v>471011</v>
       </c>
       <c r="R20" t="n">
-        <v>7140899</v>
+        <v>7140807</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2953,7 +2940,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2963,7 +2950,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2990,10 +2982,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118654949</v>
+        <v>118656619</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3025,7 +3017,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3044,13 +3036,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471177</v>
+        <v>471105</v>
       </c>
       <c r="R21" t="n">
-        <v>7140901</v>
+        <v>7140950</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3077,9 +3069,19 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3106,10 +3108,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118656647</v>
+        <v>118656092</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3118,35 +3120,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3155,10 +3153,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471105</v>
+        <v>471143</v>
       </c>
       <c r="R22" t="n">
-        <v>7140950</v>
+        <v>7141012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3190,7 +3188,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3200,12 +3198,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Va. 4 kvm med bladrosetter. Stor del mattbildande.</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3232,10 +3225,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118655326</v>
+        <v>118657609</v>
       </c>
       <c r="B23" t="n">
-        <v>57401</v>
+        <v>97853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3244,40 +3237,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3286,13 +3279,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471150</v>
+        <v>470892</v>
       </c>
       <c r="R23" t="n">
-        <v>7140890</v>
+        <v>7140851</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3321,7 +3314,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3331,7 +3324,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor/rosetter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3358,10 +3356,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118652300</v>
+        <v>118656413</v>
       </c>
       <c r="B24" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3370,31 +3368,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3403,13 +3410,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470932</v>
+        <v>471159</v>
       </c>
       <c r="R24" t="n">
-        <v>7140929</v>
+        <v>7140899</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3433,22 +3440,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minat 45 bladrosetter över ca 1 kvm yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3475,10 +3487,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118658352</v>
+        <v>118655282</v>
       </c>
       <c r="B25" t="n">
-        <v>56494</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3487,41 +3499,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3530,10 +3541,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471000</v>
+        <v>471154</v>
       </c>
       <c r="R25" t="n">
-        <v>7140830</v>
+        <v>7140912</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3563,19 +3574,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3602,7 +3603,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118654317</v>
+        <v>118652300</v>
       </c>
       <c r="B26" t="n">
         <v>57306</v>
@@ -3643,17 +3644,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471203</v>
+        <v>470932</v>
       </c>
       <c r="R26" t="n">
-        <v>7140769</v>
+        <v>7140929</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3682,7 +3683,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3692,12 +3693,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Födosök Spillkråka</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3724,10 +3720,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118655282</v>
+        <v>118655082</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3759,17 +3755,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3778,13 +3774,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471154</v>
+        <v>471177</v>
       </c>
       <c r="R27" t="n">
-        <v>7140912</v>
+        <v>7140901</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3814,6 +3810,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Över ca. 20 kvm ytan rosetter och stänglar i blom i olika fält. Även spridda rosetter i mossan.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3840,10 +3841,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118649845</v>
+        <v>118657198</v>
       </c>
       <c r="B28" t="n">
-        <v>90522</v>
+        <v>56494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3856,37 +3857,52 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471124</v>
+        <v>470996</v>
       </c>
       <c r="R28" t="n">
-        <v>7140767</v>
+        <v>7140928</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3910,22 +3926,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Järpe med ungar boplats vid vindfällen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3952,10 +3973,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118656092</v>
+        <v>118654475</v>
       </c>
       <c r="B29" t="n">
-        <v>57306</v>
+        <v>97770</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3964,31 +3985,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3997,13 +4027,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471143</v>
+        <v>471220</v>
       </c>
       <c r="R29" t="n">
-        <v>7141012</v>
+        <v>7140873</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4032,7 +4062,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4042,7 +4072,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4069,10 +4099,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118655469</v>
+        <v>118654317</v>
       </c>
       <c r="B30" t="n">
-        <v>56494</v>
+        <v>57306</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4085,16 +4115,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4102,34 +4132,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äggskal</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471147</v>
+        <v>471203</v>
       </c>
       <c r="R30" t="n">
-        <v>7140935</v>
+        <v>7140769</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4153,27 +4174,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
+          <t>Födosök Spillkråka</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4200,10 +4221,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118649741</v>
+        <v>118655326</v>
       </c>
       <c r="B31" t="n">
-        <v>90515</v>
+        <v>57401</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4216,37 +4237,51 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1205</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471038</v>
+        <v>471150</v>
       </c>
       <c r="R31" t="n">
-        <v>7140797</v>
+        <v>7140890</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4270,22 +4305,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4312,10 +4347,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118653585</v>
+        <v>118653001</v>
       </c>
       <c r="B32" t="n">
-        <v>79600</v>
+        <v>56494</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4324,41 +4359,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471126</v>
+        <v>471105</v>
       </c>
       <c r="R32" t="n">
-        <v>7140737</v>
+        <v>7140803</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4424,10 +4473,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118658808</v>
+        <v>118658352</v>
       </c>
       <c r="B33" t="n">
-        <v>97763</v>
+        <v>56494</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4436,40 +4485,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4478,13 +4528,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471124</v>
+        <v>471000</v>
       </c>
       <c r="R33" t="n">
-        <v>7140767</v>
+        <v>7140830</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4513,7 +4563,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4523,7 +4573,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4550,10 +4600,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118657609</v>
+        <v>118649845</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>90529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4562,52 +4612,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470892</v>
+        <v>471124</v>
       </c>
       <c r="R34" t="n">
-        <v>7140851</v>
+        <v>7140767</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4634,27 +4670,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor/rosetter.</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4681,10 +4712,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118657198</v>
+        <v>118658808</v>
       </c>
       <c r="B35" t="n">
-        <v>56494</v>
+        <v>97770</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4693,41 +4724,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4736,13 +4766,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>470996</v>
+        <v>471124</v>
       </c>
       <c r="R35" t="n">
-        <v>7140928</v>
+        <v>7140767</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4771,7 +4801,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4781,12 +4811,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Järpe med ungar boplats vid vindfällen</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4813,10 +4838,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118652356</v>
+        <v>118649741</v>
       </c>
       <c r="B36" t="n">
-        <v>57306</v>
+        <v>90522</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4825,46 +4850,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471011</v>
+        <v>471038</v>
       </c>
       <c r="R36" t="n">
-        <v>7140906</v>
+        <v>7140797</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4893,7 +4913,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4903,7 +4923,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4930,10 +4950,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118658516</v>
+        <v>118655469</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>56494</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4942,40 +4962,40 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äggskal</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4984,13 +5004,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471011</v>
+        <v>471147</v>
       </c>
       <c r="R37" t="n">
-        <v>7140807</v>
+        <v>7140935</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5019,7 +5039,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5029,12 +5049,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
+          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1891,7 +1891,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118611120</v>
+        <v>118611103</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1168,7 +1168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118610565</v>
+        <v>118610117</v>
       </c>
       <c r="B6" t="n">
         <v>97853</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1218,14 +1218,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håagkat (Håagkat), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471004</v>
+        <v>471181</v>
       </c>
       <c r="R6" t="n">
-        <v>7140974</v>
+        <v>7140954</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1268,6 +1268,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1284,7 +1289,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118613059</v>
+        <v>118610096</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1327,21 +1332,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat (Håagkat), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471123</v>
+        <v>471229</v>
       </c>
       <c r="R7" t="n">
-        <v>7140909</v>
+        <v>7140929</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1384,6 +1384,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1400,7 +1405,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118609933</v>
+        <v>118611120</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1435,7 +1440,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1445,19 +1450,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Håagkat (Håagkat), Jmt</t>
+          <t>Håkafot (Håkafot), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471229</v>
+        <v>470955</v>
       </c>
       <c r="R8" t="n">
-        <v>7140929</v>
+        <v>7140903</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1500,11 +1505,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118615387</v>
+        <v>118610965</v>
       </c>
       <c r="B9" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,38 +1533,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471126</v>
+        <v>471000</v>
       </c>
       <c r="R9" t="n">
-        <v>7140737</v>
+        <v>7140801</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1607,21 +1621,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1638,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118619895</v>
+        <v>118610418</v>
       </c>
       <c r="B10" t="n">
-        <v>56494</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,56 +1649,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot (Håkafot), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>471080</v>
       </c>
       <c r="R10" t="n">
-        <v>7140901</v>
+        <v>7140963</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1726,19 +1724,9 @@
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,7 +1758,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118610117</v>
+        <v>118613050</v>
       </c>
       <c r="B11" t="n">
         <v>97853</v>
@@ -1805,7 +1793,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1820,14 +1808,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håagkat (Håagkat), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471181</v>
+        <v>471123</v>
       </c>
       <c r="R11" t="n">
-        <v>7140954</v>
+        <v>7140909</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1870,11 +1858,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1891,7 +1874,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118611103</v>
+        <v>118610565</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1926,7 +1909,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1936,7 +1919,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1945,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470955</v>
+        <v>471004</v>
       </c>
       <c r="R12" t="n">
-        <v>7140903</v>
+        <v>7140974</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -2007,10 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118610965</v>
+        <v>118619895</v>
       </c>
       <c r="B13" t="n">
-        <v>97853</v>
+        <v>56494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,40 +2002,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2061,13 +2045,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471000</v>
+        <v>471080</v>
       </c>
       <c r="R13" t="n">
-        <v>7140801</v>
+        <v>7140901</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,11 +2078,21 @@
           <t>2024-07-22</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-22</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2107,6 +2101,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2123,10 +2122,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118610418</v>
+        <v>118615387</v>
       </c>
       <c r="B14" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,52 +2134,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471080</v>
+        <v>471126</v>
       </c>
       <c r="R14" t="n">
-        <v>7140963</v>
+        <v>7140737</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2224,9 +2209,19 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2370,7 +2365,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118633149</v>
+        <v>118633190</v>
       </c>
       <c r="B16" t="n">
         <v>56494</v>
@@ -2405,12 +2400,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2459,7 +2454,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,7 +2464,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,10 +2491,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118652356</v>
+        <v>118653585</v>
       </c>
       <c r="B17" t="n">
-        <v>57306</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2508,46 +2503,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471011</v>
+        <v>471126</v>
       </c>
       <c r="R17" t="n">
-        <v>7140906</v>
+        <v>7140737</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,7 +2566,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2576,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2613,7 +2603,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118656215</v>
+        <v>118655376</v>
       </c>
       <c r="B18" t="n">
         <v>97853</v>
@@ -2648,17 +2638,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2667,13 +2657,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471176</v>
+        <v>471154</v>
       </c>
       <c r="R18" t="n">
-        <v>7140877</v>
+        <v>7140912</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2702,7 +2692,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2712,7 +2702,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 500 rosetter inom ca.9 kvm yta</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,10 +2734,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118653585</v>
+        <v>118656180</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2751,38 +2746,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471126</v>
+        <v>471177</v>
       </c>
       <c r="R19" t="n">
-        <v>7140737</v>
+        <v>7140901</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2809,22 +2818,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2860,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118658516</v>
+        <v>118658808</v>
       </c>
       <c r="B20" t="n">
-        <v>97853</v>
+        <v>97770</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,40 +2872,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2905,13 +2914,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471011</v>
+        <v>471124</v>
       </c>
       <c r="R20" t="n">
-        <v>7140807</v>
+        <v>7140767</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2951,11 +2960,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2982,7 +2986,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118656619</v>
+        <v>118656647</v>
       </c>
       <c r="B21" t="n">
         <v>97853</v>
@@ -3017,17 +3021,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3082,6 +3081,11 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Va. 4 kvm med bladrosetter. Stor del mattbildande.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3108,7 +3112,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118656092</v>
+        <v>118652356</v>
       </c>
       <c r="B22" t="n">
         <v>57306</v>
@@ -3153,13 +3157,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471143</v>
+        <v>471011</v>
       </c>
       <c r="R22" t="n">
-        <v>7141012</v>
+        <v>7140906</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3183,22 +3187,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3225,10 +3229,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118657609</v>
+        <v>118654317</v>
       </c>
       <c r="B23" t="n">
-        <v>97853</v>
+        <v>57306</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3237,55 +3241,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>470892</v>
+        <v>471203</v>
       </c>
       <c r="R23" t="n">
-        <v>7140851</v>
+        <v>7140769</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3309,27 +3304,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 14 plantor/rosetter.</t>
+          <t>Födosök Spillkråka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3356,10 +3351,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118656413</v>
+        <v>118655326</v>
       </c>
       <c r="B24" t="n">
-        <v>97853</v>
+        <v>57401</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3368,40 +3363,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3410,13 +3405,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471159</v>
+        <v>471150</v>
       </c>
       <c r="R24" t="n">
-        <v>7140899</v>
+        <v>7140890</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3445,7 +3440,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3455,12 +3450,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minat 45 bladrosetter över ca 1 kvm yta.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3487,10 +3477,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118655282</v>
+        <v>118657198</v>
       </c>
       <c r="B25" t="n">
-        <v>97853</v>
+        <v>56494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3499,40 +3489,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3541,13 +3532,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471154</v>
+        <v>470996</v>
       </c>
       <c r="R25" t="n">
-        <v>7140912</v>
+        <v>7140928</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3574,9 +3565,24 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Järpe med ungar boplats vid vindfällen</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,10 +3609,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118652300</v>
+        <v>118658352</v>
       </c>
       <c r="B26" t="n">
-        <v>57306</v>
+        <v>56494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3619,16 +3625,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3637,9 +3643,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3648,13 +3664,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>470932</v>
+        <v>471000</v>
       </c>
       <c r="R26" t="n">
-        <v>7140929</v>
+        <v>7140830</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3678,22 +3694,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3720,7 +3736,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118655082</v>
+        <v>118656490</v>
       </c>
       <c r="B27" t="n">
         <v>97853</v>
@@ -3774,13 +3790,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471177</v>
+        <v>471159</v>
       </c>
       <c r="R27" t="n">
-        <v>7140901</v>
+        <v>7140899</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3807,14 +3823,24 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Över ca. 20 kvm ytan rosetter och stänglar i blom i olika fält. Även spridda rosetter i mossan.</t>
+          <t>15-20 kvm stor yta beväxt med bladeosetter många sjok mattbildande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3841,7 +3867,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118657198</v>
+        <v>118653001</v>
       </c>
       <c r="B28" t="n">
         <v>56494</v>
@@ -3874,20 +3900,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>pulli</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3896,10 +3921,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>470996</v>
+        <v>471105</v>
       </c>
       <c r="R28" t="n">
-        <v>7140928</v>
+        <v>7140803</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3926,7 +3951,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3936,17 +3961,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
           <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Järpe med ungar boplats vid vindfällen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3973,10 +3993,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118654475</v>
+        <v>118656092</v>
       </c>
       <c r="B29" t="n">
-        <v>97770</v>
+        <v>57306</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3985,40 +4005,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4027,13 +4038,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471220</v>
+        <v>471143</v>
       </c>
       <c r="R29" t="n">
-        <v>7140873</v>
+        <v>7141012</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4062,7 +4073,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4072,7 +4083,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4099,10 +4110,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118654317</v>
+        <v>118657575</v>
       </c>
       <c r="B30" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4111,46 +4122,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471203</v>
+        <v>470892</v>
       </c>
       <c r="R30" t="n">
-        <v>7140769</v>
+        <v>7140851</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4174,27 +4194,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Födosök Spillkråka</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4221,10 +4236,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118655326</v>
+        <v>118649741</v>
       </c>
       <c r="B31" t="n">
-        <v>57401</v>
+        <v>90522</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4237,51 +4252,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>1205</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471150</v>
+        <v>471038</v>
       </c>
       <c r="R31" t="n">
-        <v>7140890</v>
+        <v>7140797</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4305,22 +4306,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4347,10 +4348,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118653001</v>
+        <v>118656249</v>
       </c>
       <c r="B32" t="n">
-        <v>56494</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4359,40 +4360,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4401,10 +4397,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471105</v>
+        <v>471176</v>
       </c>
       <c r="R32" t="n">
-        <v>7140803</v>
+        <v>7140877</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4431,22 +4427,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca. 1 kvm syntliga rosetter. Mattbildande.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4473,10 +4474,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118658352</v>
+        <v>118654541</v>
       </c>
       <c r="B33" t="n">
-        <v>56494</v>
+        <v>97770</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4485,41 +4486,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4528,13 +4528,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471000</v>
+        <v>471220</v>
       </c>
       <c r="R33" t="n">
-        <v>7140830</v>
+        <v>7140873</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4558,22 +4558,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4600,10 +4600,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118649845</v>
+        <v>118658516</v>
       </c>
       <c r="B34" t="n">
-        <v>90529</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4612,41 +4612,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471124</v>
+        <v>471011</v>
       </c>
       <c r="R34" t="n">
-        <v>7140767</v>
+        <v>7140807</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4670,22 +4684,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4712,10 +4731,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118658808</v>
+        <v>118652300</v>
       </c>
       <c r="B35" t="n">
-        <v>97770</v>
+        <v>57306</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4724,40 +4743,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4766,13 +4776,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471124</v>
+        <v>470932</v>
       </c>
       <c r="R35" t="n">
-        <v>7140767</v>
+        <v>7140929</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4796,22 +4806,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4838,10 +4848,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118649741</v>
+        <v>118649845</v>
       </c>
       <c r="B36" t="n">
-        <v>90522</v>
+        <v>90529</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4850,25 +4860,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4878,13 +4888,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471038</v>
+        <v>471124</v>
       </c>
       <c r="R36" t="n">
-        <v>7140797</v>
+        <v>7140767</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5329,10 +5329,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119787378</v>
+        <v>119787342</v>
       </c>
       <c r="B40" t="n">
-        <v>86289</v>
+        <v>86334</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5341,25 +5341,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119787342</v>
+        <v>119787378</v>
       </c>
       <c r="B41" t="n">
-        <v>86334</v>
+        <v>86289</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5447,25 +5447,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5329,10 +5329,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119787342</v>
+        <v>119787378</v>
       </c>
       <c r="B40" t="n">
-        <v>86334</v>
+        <v>86289</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5341,25 +5341,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119787378</v>
+        <v>119787342</v>
       </c>
       <c r="B41" t="n">
-        <v>86289</v>
+        <v>86334</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5447,25 +5447,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5329,10 +5329,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119787378</v>
+        <v>119787342</v>
       </c>
       <c r="B40" t="n">
-        <v>86289</v>
+        <v>86351</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5341,25 +5341,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119787342</v>
+        <v>119787378</v>
       </c>
       <c r="B41" t="n">
-        <v>86334</v>
+        <v>86306</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5447,25 +5447,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5336,7 +5336,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5539,6 +5539,259 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122603183</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56585</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>471073</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7140813</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122603006</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>470980</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7140865</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5541,10 +5541,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122603183</v>
+        <v>122603006</v>
       </c>
       <c r="B42" t="n">
-        <v>56585</v>
+        <v>57383</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5557,16 +5557,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5574,24 +5574,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5600,13 +5591,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471073</v>
+        <v>470980</v>
       </c>
       <c r="R42" t="n">
-        <v>7140813</v>
+        <v>7140865</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5640,7 +5631,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5672,10 +5663,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122603006</v>
+        <v>122603183</v>
       </c>
       <c r="B43" t="n">
-        <v>57383</v>
+        <v>56585</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5688,16 +5679,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5705,15 +5696,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>470980</v>
+        <v>471073</v>
       </c>
       <c r="R43" t="n">
-        <v>7140865</v>
+        <v>7140813</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5541,10 +5541,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122603006</v>
+        <v>122603183</v>
       </c>
       <c r="B42" t="n">
-        <v>57383</v>
+        <v>56585</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5557,16 +5557,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5574,15 +5574,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5591,13 +5600,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>470980</v>
+        <v>471073</v>
       </c>
       <c r="R42" t="n">
-        <v>7140865</v>
+        <v>7140813</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5631,7 +5640,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5663,10 +5672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122603183</v>
+        <v>122603006</v>
       </c>
       <c r="B43" t="n">
-        <v>56585</v>
+        <v>57383</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5679,16 +5688,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5696,24 +5705,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471073</v>
+        <v>470980</v>
       </c>
       <c r="R43" t="n">
-        <v>7140813</v>
+        <v>7140865</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5541,10 +5541,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122603183</v>
+        <v>122603006</v>
       </c>
       <c r="B42" t="n">
-        <v>56585</v>
+        <v>57384</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5557,16 +5557,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5574,24 +5574,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5600,13 +5591,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471073</v>
+        <v>470980</v>
       </c>
       <c r="R42" t="n">
-        <v>7140813</v>
+        <v>7140865</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5640,7 +5631,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5672,10 +5663,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122603006</v>
+        <v>122603183</v>
       </c>
       <c r="B43" t="n">
-        <v>57383</v>
+        <v>56586</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5688,16 +5679,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5705,15 +5696,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>470980</v>
+        <v>471073</v>
       </c>
       <c r="R43" t="n">
-        <v>7140865</v>
+        <v>7140813</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5541,10 +5541,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122603006</v>
+        <v>122603183</v>
       </c>
       <c r="B42" t="n">
-        <v>57384</v>
+        <v>56586</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5557,16 +5557,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5574,15 +5574,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5591,13 +5600,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>470980</v>
+        <v>471073</v>
       </c>
       <c r="R42" t="n">
-        <v>7140865</v>
+        <v>7140813</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5631,7 +5640,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5663,10 +5672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122603183</v>
+        <v>122603006</v>
       </c>
       <c r="B43" t="n">
-        <v>56586</v>
+        <v>57384</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5679,16 +5688,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5696,24 +5705,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471073</v>
+        <v>470980</v>
       </c>
       <c r="R43" t="n">
-        <v>7140813</v>
+        <v>7140865</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5541,10 +5541,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122603183</v>
+        <v>122603006</v>
       </c>
       <c r="B42" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5557,16 +5557,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5574,24 +5574,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5600,13 +5591,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471073</v>
+        <v>470980</v>
       </c>
       <c r="R42" t="n">
-        <v>7140813</v>
+        <v>7140865</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5640,7 +5631,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5672,10 +5663,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122603006</v>
+        <v>122603183</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5688,16 +5679,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5705,15 +5696,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>470980</v>
+        <v>471073</v>
       </c>
       <c r="R43" t="n">
-        <v>7140865</v>
+        <v>7140813</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5541,10 +5541,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122603006</v>
+        <v>122603183</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5557,16 +5557,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5574,15 +5574,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5591,13 +5600,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>470980</v>
+        <v>471073</v>
       </c>
       <c r="R42" t="n">
-        <v>7140865</v>
+        <v>7140813</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5631,7 +5640,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5663,10 +5672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122603183</v>
+        <v>122603006</v>
       </c>
       <c r="B43" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5679,16 +5688,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5696,24 +5705,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471073</v>
+        <v>470980</v>
       </c>
       <c r="R43" t="n">
-        <v>7140813</v>
+        <v>7140865</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5541,10 +5541,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122603006</v>
+        <v>122603183</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5557,16 +5557,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5574,15 +5574,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5591,13 +5600,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>470980</v>
+        <v>471073</v>
       </c>
       <c r="R42" t="n">
-        <v>7140865</v>
+        <v>7140813</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5631,7 +5640,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5663,14 +5672,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122603183</v>
+        <v>122603006</v>
       </c>
       <c r="B43" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5679,16 +5688,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5696,24 +5705,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471073</v>
+        <v>470980</v>
       </c>
       <c r="R43" t="n">
-        <v>7140813</v>
+        <v>7140865</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5792,6 +5792,573 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123377834</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Håkafot, Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>471007</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7141045</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Tydliga färska födosök spillkråka</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123377704</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90970</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Håkafot, Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>471020</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7141049</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123377064</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Håagkat, Håagkat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>471175</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7140991</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123377276</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Håkafot, Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>471094</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7141017</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123377514</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Håkafot, Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>471066</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7141025</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5675,7 +5675,7 @@
         <v>122603006</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>123377834</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5906,10 +5906,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123377704</v>
+        <v>123377276</v>
       </c>
       <c r="B45" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5922,36 +5922,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5960,10 +5955,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471020</v>
+        <v>471094</v>
       </c>
       <c r="R45" t="n">
-        <v>7141049</v>
+        <v>7141017</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5996,6 +5991,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6025,7 +6025,7 @@
         <v>123377064</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6129,10 +6129,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377276</v>
+        <v>123377514</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471094</v>
+        <v>471066</v>
       </c>
       <c r="R47" t="n">
-        <v>7141017</v>
+        <v>7141025</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6245,10 +6245,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123377514</v>
+        <v>123377704</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>90973</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6261,31 +6261,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6294,10 +6299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471066</v>
+        <v>471020</v>
       </c>
       <c r="R48" t="n">
-        <v>7141025</v>
+        <v>7141049</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6330,11 +6335,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5794,10 +5794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123377834</v>
+        <v>123377064</v>
       </c>
       <c r="B44" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5828,21 +5828,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471007</v>
+        <v>471175</v>
       </c>
       <c r="R44" t="n">
-        <v>7141045</v>
+        <v>7140991</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5879,7 +5874,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5906,10 +5901,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123377276</v>
+        <v>123377834</v>
       </c>
       <c r="B45" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5922,16 +5917,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5939,11 +5934,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -5955,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471094</v>
+        <v>471007</v>
       </c>
       <c r="R45" t="n">
-        <v>7141017</v>
+        <v>7141045</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5995,7 +5986,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6022,7 +6013,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377064</v>
+        <v>123377276</v>
       </c>
       <c r="B46" t="n">
         <v>57481</v>
@@ -6055,17 +6046,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471175</v>
+        <v>471094</v>
       </c>
       <c r="R46" t="n">
-        <v>7140991</v>
+        <v>7141017</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6129,10 +6129,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377514</v>
+        <v>123377704</v>
       </c>
       <c r="B47" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6145,31 +6145,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6178,10 +6183,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471066</v>
+        <v>471020</v>
       </c>
       <c r="R47" t="n">
-        <v>7141025</v>
+        <v>7141049</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6214,11 +6219,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6245,10 +6245,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123377704</v>
+        <v>123377514</v>
       </c>
       <c r="B48" t="n">
-        <v>90973</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6261,36 +6261,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6299,10 +6294,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471020</v>
+        <v>471066</v>
       </c>
       <c r="R48" t="n">
-        <v>7141049</v>
+        <v>7141025</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6335,6 +6330,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5794,10 +5794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123377064</v>
+        <v>123377834</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5828,16 +5828,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471175</v>
+        <v>471007</v>
       </c>
       <c r="R44" t="n">
-        <v>7140991</v>
+        <v>7141045</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5874,7 +5879,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5901,10 +5906,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123377834</v>
+        <v>123377276</v>
       </c>
       <c r="B45" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5917,16 +5922,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5934,7 +5939,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -5946,10 +5955,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471007</v>
+        <v>471094</v>
       </c>
       <c r="R45" t="n">
-        <v>7141045</v>
+        <v>7141017</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5986,7 +5995,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6013,7 +6022,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377276</v>
+        <v>123377064</v>
       </c>
       <c r="B46" t="n">
         <v>57481</v>
@@ -6046,26 +6055,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471094</v>
+        <v>471175</v>
       </c>
       <c r="R46" t="n">
-        <v>7141017</v>
+        <v>7140991</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6129,10 +6129,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377704</v>
+        <v>123377514</v>
       </c>
       <c r="B47" t="n">
-        <v>90975</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6145,36 +6145,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6183,10 +6178,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471020</v>
+        <v>471066</v>
       </c>
       <c r="R47" t="n">
-        <v>7141049</v>
+        <v>7141025</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6219,6 +6214,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6245,10 +6245,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123377514</v>
+        <v>123377704</v>
       </c>
       <c r="B48" t="n">
-        <v>57481</v>
+        <v>90981</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6261,31 +6261,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6294,10 +6299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471066</v>
+        <v>471020</v>
       </c>
       <c r="R48" t="n">
-        <v>7141025</v>
+        <v>7141049</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6330,11 +6335,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5794,10 +5794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123377834</v>
+        <v>123377064</v>
       </c>
       <c r="B44" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5828,21 +5828,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471007</v>
+        <v>471175</v>
       </c>
       <c r="R44" t="n">
-        <v>7141045</v>
+        <v>7140991</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5879,7 +5874,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5906,10 +5901,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123377276</v>
+        <v>123377834</v>
       </c>
       <c r="B45" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5922,16 +5917,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5939,11 +5934,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -5955,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471094</v>
+        <v>471007</v>
       </c>
       <c r="R45" t="n">
-        <v>7141017</v>
+        <v>7141045</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5995,7 +5986,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6022,7 +6013,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377064</v>
+        <v>123377276</v>
       </c>
       <c r="B46" t="n">
         <v>57481</v>
@@ -6055,17 +6046,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471175</v>
+        <v>471094</v>
       </c>
       <c r="R46" t="n">
-        <v>7140991</v>
+        <v>7141017</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6248,7 +6248,7 @@
         <v>123377704</v>
       </c>
       <c r="B48" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5675,7 +5675,7 @@
         <v>122603006</v>
       </c>
       <c r="B43" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>123377064</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123377834</v>
+        <v>123377514</v>
       </c>
       <c r="B45" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5917,16 +5917,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5934,7 +5934,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -5946,10 +5950,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471007</v>
+        <v>471066</v>
       </c>
       <c r="R45" t="n">
-        <v>7141045</v>
+        <v>7141025</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5986,7 +5990,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6013,10 +6017,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377276</v>
+        <v>123377834</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>57503</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6029,16 +6033,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6046,11 +6050,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471094</v>
+        <v>471007</v>
       </c>
       <c r="R46" t="n">
-        <v>7141017</v>
+        <v>7141045</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6129,10 +6129,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377514</v>
+        <v>123377276</v>
       </c>
       <c r="B47" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471066</v>
+        <v>471094</v>
       </c>
       <c r="R47" t="n">
-        <v>7141025</v>
+        <v>7141017</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6242,122 +6242,6 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>123377704</v>
-      </c>
-      <c r="B48" t="n">
-        <v>90984</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Håkafot, Håkafot, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>471020</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7141049</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5675,7 +5675,7 @@
         <v>122603006</v>
       </c>
       <c r="B43" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123377064</v>
+        <v>123377834</v>
       </c>
       <c r="B44" t="n">
-        <v>57487</v>
+        <v>57506</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5828,16 +5828,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471175</v>
+        <v>471007</v>
       </c>
       <c r="R44" t="n">
-        <v>7140991</v>
+        <v>7141045</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5874,7 +5879,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5904,7 +5909,7 @@
         <v>123377514</v>
       </c>
       <c r="B45" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6017,10 +6022,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377834</v>
+        <v>123377276</v>
       </c>
       <c r="B46" t="n">
-        <v>57503</v>
+        <v>57490</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6033,16 +6038,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6050,7 +6055,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6062,10 +6071,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471007</v>
+        <v>471094</v>
       </c>
       <c r="R46" t="n">
-        <v>7141045</v>
+        <v>7141017</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6111,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6129,10 +6138,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377276</v>
+        <v>123377064</v>
       </c>
       <c r="B47" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6162,26 +6171,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471094</v>
+        <v>471175</v>
       </c>
       <c r="R47" t="n">
-        <v>7141017</v>
+        <v>7140991</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5675,7 +5675,7 @@
         <v>122603006</v>
       </c>
       <c r="B43" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123377834</v>
+        <v>123377064</v>
       </c>
       <c r="B44" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5828,21 +5828,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471007</v>
+        <v>471175</v>
       </c>
       <c r="R44" t="n">
-        <v>7141045</v>
+        <v>7140991</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5879,7 +5874,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5906,10 +5901,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123377514</v>
+        <v>123377834</v>
       </c>
       <c r="B45" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5922,16 +5917,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5939,11 +5934,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -5955,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471066</v>
+        <v>471007</v>
       </c>
       <c r="R45" t="n">
-        <v>7141025</v>
+        <v>7141045</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5995,7 +5986,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6022,10 +6013,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377276</v>
+        <v>123377514</v>
       </c>
       <c r="B46" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6071,10 +6062,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471094</v>
+        <v>471066</v>
       </c>
       <c r="R46" t="n">
-        <v>7141017</v>
+        <v>7141025</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6111,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6138,10 +6129,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377064</v>
+        <v>123377276</v>
       </c>
       <c r="B47" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6171,17 +6162,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471175</v>
+        <v>471094</v>
       </c>
       <c r="R47" t="n">
-        <v>7140991</v>
+        <v>7141017</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -6013,7 +6013,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377514</v>
+        <v>123377276</v>
       </c>
       <c r="B46" t="n">
         <v>57491</v>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471066</v>
+        <v>471094</v>
       </c>
       <c r="R46" t="n">
-        <v>7141025</v>
+        <v>7141017</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6129,7 +6129,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377276</v>
+        <v>123377514</v>
       </c>
       <c r="B47" t="n">
         <v>57491</v>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471094</v>
+        <v>471066</v>
       </c>
       <c r="R47" t="n">
-        <v>7141017</v>
+        <v>7141025</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5901,10 +5901,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123377834</v>
+        <v>123377276</v>
       </c>
       <c r="B45" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5917,16 +5917,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5934,7 +5934,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -5946,10 +5950,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471007</v>
+        <v>471094</v>
       </c>
       <c r="R45" t="n">
-        <v>7141045</v>
+        <v>7141017</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5986,7 +5990,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6013,10 +6017,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377276</v>
+        <v>123377834</v>
       </c>
       <c r="B46" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6029,16 +6033,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6046,11 +6050,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471094</v>
+        <v>471007</v>
       </c>
       <c r="R46" t="n">
-        <v>7141017</v>
+        <v>7141045</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5794,10 +5794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123377064</v>
+        <v>123377834</v>
       </c>
       <c r="B44" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5828,16 +5828,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471175</v>
+        <v>471007</v>
       </c>
       <c r="R44" t="n">
-        <v>7140991</v>
+        <v>7141045</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5874,7 +5879,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6017,10 +6022,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377834</v>
+        <v>123377064</v>
       </c>
       <c r="B46" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6033,16 +6038,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6051,21 +6056,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471007</v>
+        <v>471175</v>
       </c>
       <c r="R46" t="n">
-        <v>7141045</v>
+        <v>7140991</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5794,10 +5794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123377834</v>
+        <v>123377064</v>
       </c>
       <c r="B44" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5828,21 +5828,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471007</v>
+        <v>471175</v>
       </c>
       <c r="R44" t="n">
-        <v>7141045</v>
+        <v>7140991</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5879,7 +5874,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6022,7 +6017,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377064</v>
+        <v>123377514</v>
       </c>
       <c r="B46" t="n">
         <v>57491</v>
@@ -6055,17 +6050,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471175</v>
+        <v>471066</v>
       </c>
       <c r="R46" t="n">
-        <v>7140991</v>
+        <v>7141025</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6106,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6129,10 +6133,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377514</v>
+        <v>123377834</v>
       </c>
       <c r="B47" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6145,16 +6149,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6162,11 +6166,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471066</v>
+        <v>471007</v>
       </c>
       <c r="R47" t="n">
-        <v>7141025</v>
+        <v>7141045</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -6017,10 +6017,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377514</v>
+        <v>123377834</v>
       </c>
       <c r="B46" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6033,16 +6033,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6050,11 +6050,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6066,10 +6062,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471066</v>
+        <v>471007</v>
       </c>
       <c r="R46" t="n">
-        <v>7141025</v>
+        <v>7141045</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6106,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6133,10 +6129,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377834</v>
+        <v>123377514</v>
       </c>
       <c r="B47" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6149,16 +6145,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6166,7 +6162,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471007</v>
+        <v>471066</v>
       </c>
       <c r="R47" t="n">
-        <v>7141045</v>
+        <v>7141025</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -5794,10 +5794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123377064</v>
+        <v>123377834</v>
       </c>
       <c r="B44" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5828,16 +5828,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471175</v>
+        <v>471007</v>
       </c>
       <c r="R44" t="n">
-        <v>7140991</v>
+        <v>7141045</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5874,7 +5879,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5901,7 +5906,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123377276</v>
+        <v>123377064</v>
       </c>
       <c r="B45" t="n">
         <v>57491</v>
@@ -5934,26 +5939,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471094</v>
+        <v>471175</v>
       </c>
       <c r="R45" t="n">
-        <v>7141017</v>
+        <v>7140991</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5990,7 +5986,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6017,10 +6013,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377834</v>
+        <v>123377514</v>
       </c>
       <c r="B46" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6033,16 +6029,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6050,7 +6046,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471007</v>
+        <v>471066</v>
       </c>
       <c r="R46" t="n">
-        <v>7141045</v>
+        <v>7141025</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6129,7 +6129,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377514</v>
+        <v>123377276</v>
       </c>
       <c r="B47" t="n">
         <v>57491</v>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471066</v>
+        <v>471094</v>
       </c>
       <c r="R47" t="n">
-        <v>7141025</v>
+        <v>7141017</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6243,6 +6243,1308 @@
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126267316</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98262</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>471000</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7140801</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126265620</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>470985</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7141047</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126266135</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>470925</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7141000</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126266486</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98262</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>470908</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7140946</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126273173</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>470992</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7140849</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126266106</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98262</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>470925</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7141000</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126266225</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>470925</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7141000</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126264186</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>470971</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7140842</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126266654</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98262</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>470901</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7140921</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126266987</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98262</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>470927</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7140793</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126264597</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>470938</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7141021</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -7068,10 +7068,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126264186</v>
+        <v>126266654</v>
       </c>
       <c r="B55" t="n">
-        <v>98366</v>
+        <v>98262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7079,26 +7079,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7106,21 +7106,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470971</v>
+        <v>470901</v>
       </c>
       <c r="R55" t="n">
-        <v>7140842</v>
+        <v>7140921</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7152,7 +7147,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7162,7 +7157,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7189,10 +7184,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126266654</v>
+        <v>126264186</v>
       </c>
       <c r="B56" t="n">
-        <v>98262</v>
+        <v>98366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7200,26 +7195,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7227,16 +7222,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470901</v>
+        <v>470971</v>
       </c>
       <c r="R56" t="n">
-        <v>7140921</v>
+        <v>7140842</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -6248,7 +6248,7 @@
         <v>126267316</v>
       </c>
       <c r="B48" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>126265620</v>
       </c>
       <c r="B49" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>126266135</v>
       </c>
       <c r="B50" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>126266486</v>
       </c>
       <c r="B51" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>126273173</v>
       </c>
       <c r="B52" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126266106</v>
+        <v>126266225</v>
       </c>
       <c r="B53" t="n">
-        <v>98262</v>
+        <v>98253</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6837,26 +6837,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6947,10 +6947,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126266225</v>
+        <v>126266106</v>
       </c>
       <c r="B54" t="n">
-        <v>98249</v>
+        <v>98266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6958,26 +6958,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7068,10 +7068,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126266654</v>
+        <v>126264186</v>
       </c>
       <c r="B55" t="n">
-        <v>98262</v>
+        <v>98370</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7079,26 +7079,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7106,16 +7106,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470901</v>
+        <v>470971</v>
       </c>
       <c r="R55" t="n">
-        <v>7140921</v>
+        <v>7140842</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7147,7 +7152,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7157,7 +7162,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7184,10 +7189,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126264186</v>
+        <v>126266654</v>
       </c>
       <c r="B56" t="n">
-        <v>98366</v>
+        <v>98266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7195,26 +7200,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7222,21 +7227,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470971</v>
+        <v>470901</v>
       </c>
       <c r="R56" t="n">
-        <v>7140842</v>
+        <v>7140921</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7308,7 +7308,7 @@
         <v>126266987</v>
       </c>
       <c r="B57" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>126264597</v>
       </c>
       <c r="B58" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -6248,7 +6248,7 @@
         <v>126267316</v>
       </c>
       <c r="B48" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>126266135</v>
       </c>
       <c r="B50" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>126266486</v>
       </c>
       <c r="B51" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>126273173</v>
       </c>
       <c r="B52" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126266225</v>
+        <v>126266106</v>
       </c>
       <c r="B53" t="n">
-        <v>98253</v>
+        <v>98269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6837,26 +6837,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6947,10 +6947,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126266106</v>
+        <v>126266225</v>
       </c>
       <c r="B54" t="n">
-        <v>98266</v>
+        <v>98256</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6958,26 +6958,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7068,10 +7068,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126264186</v>
+        <v>126266654</v>
       </c>
       <c r="B55" t="n">
-        <v>98370</v>
+        <v>98269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7079,26 +7079,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7106,21 +7106,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470971</v>
+        <v>470901</v>
       </c>
       <c r="R55" t="n">
-        <v>7140842</v>
+        <v>7140921</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7152,7 +7147,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7162,7 +7157,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7189,10 +7184,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126266654</v>
+        <v>126264186</v>
       </c>
       <c r="B56" t="n">
-        <v>98266</v>
+        <v>98373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7200,26 +7195,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7227,16 +7222,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470901</v>
+        <v>470971</v>
       </c>
       <c r="R56" t="n">
-        <v>7140921</v>
+        <v>7140842</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7305,10 +7305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126266987</v>
+        <v>126264597</v>
       </c>
       <c r="B57" t="n">
-        <v>98266</v>
+        <v>98373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7316,26 +7316,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>470927</v>
+        <v>470938</v>
       </c>
       <c r="R57" t="n">
-        <v>7140793</v>
+        <v>7141021</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7426,10 +7426,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126264597</v>
+        <v>126266987</v>
       </c>
       <c r="B58" t="n">
-        <v>98370</v>
+        <v>98269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7437,26 +7437,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470938</v>
+        <v>470927</v>
       </c>
       <c r="R58" t="n">
-        <v>7141021</v>
+        <v>7140793</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -7305,10 +7305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126264597</v>
+        <v>126266987</v>
       </c>
       <c r="B57" t="n">
-        <v>98373</v>
+        <v>98269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7316,26 +7316,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>470938</v>
+        <v>470927</v>
       </c>
       <c r="R57" t="n">
-        <v>7141021</v>
+        <v>7140793</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7426,10 +7426,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126266987</v>
+        <v>126264597</v>
       </c>
       <c r="B58" t="n">
-        <v>98269</v>
+        <v>98373</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7437,26 +7437,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470927</v>
+        <v>470938</v>
       </c>
       <c r="R58" t="n">
-        <v>7140793</v>
+        <v>7141021</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -7305,10 +7305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126266987</v>
+        <v>126264597</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
+        <v>98373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7316,26 +7316,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>470927</v>
+        <v>470938</v>
       </c>
       <c r="R57" t="n">
-        <v>7140793</v>
+        <v>7141021</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7426,10 +7426,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126264597</v>
+        <v>126266987</v>
       </c>
       <c r="B58" t="n">
-        <v>98373</v>
+        <v>98269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7437,26 +7437,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470938</v>
+        <v>470927</v>
       </c>
       <c r="R58" t="n">
-        <v>7141021</v>
+        <v>7140793</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -6248,7 +6248,7 @@
         <v>126267316</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>126265620</v>
       </c>
       <c r="B49" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>126266135</v>
       </c>
       <c r="B50" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>126266486</v>
       </c>
       <c r="B51" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>126273173</v>
       </c>
       <c r="B52" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126266106</v>
+        <v>126266225</v>
       </c>
       <c r="B53" t="n">
-        <v>98269</v>
+        <v>98265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6837,26 +6837,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6947,10 +6947,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126266225</v>
+        <v>126266106</v>
       </c>
       <c r="B54" t="n">
-        <v>98256</v>
+        <v>98278</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6958,26 +6958,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7071,7 +7071,7 @@
         <v>126266654</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>126264186</v>
       </c>
       <c r="B56" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7305,10 +7305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126264597</v>
+        <v>126266987</v>
       </c>
       <c r="B57" t="n">
-        <v>98373</v>
+        <v>98278</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7316,26 +7316,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>470938</v>
+        <v>470927</v>
       </c>
       <c r="R57" t="n">
-        <v>7141021</v>
+        <v>7140793</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7426,10 +7426,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126266987</v>
+        <v>126264597</v>
       </c>
       <c r="B58" t="n">
-        <v>98269</v>
+        <v>98382</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7437,26 +7437,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470927</v>
+        <v>470938</v>
       </c>
       <c r="R58" t="n">
-        <v>7140793</v>
+        <v>7141021</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8298,7 +8298,7 @@
         <v>126781777</v>
       </c>
       <c r="B65" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126782391</v>
       </c>
       <c r="B66" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8298,7 +8298,7 @@
         <v>126781777</v>
       </c>
       <c r="B65" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126782391</v>
       </c>
       <c r="B66" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -7809,10 +7809,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126783407</v>
+        <v>126782282</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>56840</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7820,16 +7820,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7837,10 +7837,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7849,13 +7863,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471028</v>
+        <v>470941</v>
       </c>
       <c r="R61" t="n">
-        <v>7140823</v>
+        <v>7140824</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7884,7 +7898,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7894,12 +7908,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7926,10 +7940,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126782282</v>
+        <v>126783407</v>
       </c>
       <c r="B62" t="n">
-        <v>56840</v>
+        <v>57657</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7937,16 +7951,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7954,24 +7968,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7980,13 +7980,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470941</v>
+        <v>471028</v>
       </c>
       <c r="R62" t="n">
-        <v>7140824</v>
+        <v>7140823</v>
       </c>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8298,7 +8298,7 @@
         <v>126781777</v>
       </c>
       <c r="B65" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126782391</v>
       </c>
       <c r="B66" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -7809,10 +7809,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126782282</v>
+        <v>126783407</v>
       </c>
       <c r="B61" t="n">
-        <v>56840</v>
+        <v>57657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7820,16 +7820,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7837,24 +7837,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7863,13 +7849,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>470941</v>
+        <v>471028</v>
       </c>
       <c r="R61" t="n">
-        <v>7140824</v>
+        <v>7140823</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7898,7 +7884,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7908,12 +7894,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7940,10 +7926,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126783407</v>
+        <v>126782282</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>56840</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7951,16 +7937,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7968,10 +7954,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7980,13 +7980,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471028</v>
+        <v>470941</v>
       </c>
       <c r="R62" t="n">
-        <v>7140823</v>
+        <v>7140824</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -7809,10 +7809,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126783407</v>
+        <v>126782282</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>56840</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7820,16 +7820,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7837,10 +7837,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7849,13 +7863,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471028</v>
+        <v>470941</v>
       </c>
       <c r="R61" t="n">
-        <v>7140823</v>
+        <v>7140824</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7884,7 +7898,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7894,12 +7908,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7926,67 +7940,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126782282</v>
+        <v>126781777</v>
       </c>
       <c r="B62" t="n">
-        <v>56840</v>
+        <v>98464</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470941</v>
+        <v>470980</v>
       </c>
       <c r="R62" t="n">
-        <v>7140824</v>
+        <v>7140865</v>
       </c>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8026,11 +8021,6 @@
       <c r="AB62" t="inlineStr">
         <is>
           <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8057,43 +8047,47 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126786066</v>
+        <v>126782391</v>
       </c>
       <c r="B63" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8102,13 +8096,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470941</v>
+        <v>470927</v>
       </c>
       <c r="R63" t="n">
-        <v>7140824</v>
+        <v>7140809</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8135,14 +8129,19 @@
           <t>2025-07-20</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-20</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Födosökande tretå i lämplig häckningsbiotop. Precis bredvid är en gran med färska samt äldre ringhack. dessutom finns flertalet födosökspår färska samt äldre och ringhackade granar med färska samt äldre ringhack. Tretå har observerats i området året runt i flera år.</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8153,11 +8152,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8174,7 +8168,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126785249</v>
+        <v>126783407</v>
       </c>
       <c r="B64" t="n">
         <v>57657</v>
@@ -8202,14 +8196,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8218,10 +8208,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>470934</v>
+        <v>471028</v>
       </c>
       <c r="R64" t="n">
-        <v>7140818</v>
+        <v>7140823</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8253,7 +8243,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8263,12 +8253,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
+          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8295,48 +8285,58 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126781777</v>
+        <v>126786066</v>
       </c>
       <c r="B65" t="n">
-        <v>98464</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>470980</v>
+        <v>470941</v>
       </c>
       <c r="R65" t="n">
-        <v>7140865</v>
+        <v>7140824</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8363,19 +8363,14 @@
           <t>2025-07-20</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-20</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:35</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Födosökande tretå i lämplig häckningsbiotop. Precis bredvid är en gran med färska samt äldre ringhack. dessutom finns flertalet födosökspår färska samt äldre och ringhackade granar med färska samt äldre ringhack. Tretå har observerats i området året runt i flera år.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8386,6 +8381,11 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8402,47 +8402,42 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126782391</v>
+        <v>126785249</v>
       </c>
       <c r="B66" t="n">
-        <v>98360</v>
+        <v>57657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8451,10 +8446,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470927</v>
+        <v>470934</v>
       </c>
       <c r="R66" t="n">
-        <v>7140809</v>
+        <v>7140818</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8486,7 +8481,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8496,7 +8491,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -7550,7 +7550,7 @@
         <v>126782070</v>
       </c>
       <c r="B59" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>126782095</v>
       </c>
       <c r="B60" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>126782282</v>
       </c>
       <c r="B61" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>126781777</v>
       </c>
       <c r="B62" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>126782391</v>
       </c>
       <c r="B63" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>126783407</v>
       </c>
       <c r="B64" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>126786066</v>
       </c>
       <c r="B65" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126785249</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8171,7 +8171,7 @@
         <v>126783407</v>
       </c>
       <c r="B64" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>126786066</v>
       </c>
       <c r="B65" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126785249</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8171,7 +8171,7 @@
         <v>126783407</v>
       </c>
       <c r="B64" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>126786066</v>
       </c>
       <c r="B65" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126785249</v>
       </c>
       <c r="B66" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8171,7 +8171,7 @@
         <v>126783407</v>
       </c>
       <c r="B64" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>126786066</v>
       </c>
       <c r="B65" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126785249</v>
       </c>
       <c r="B66" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8521,6 +8521,118 @@
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128157802</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Håagkat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>471213</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7140791</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8526,7 +8526,7 @@
         <v>128157802</v>
       </c>
       <c r="B67" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8526,7 +8526,7 @@
         <v>128157802</v>
       </c>
       <c r="B67" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,10 +8523,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128157802</v>
+        <v>128051879</v>
       </c>
       <c r="B67" t="n">
-        <v>57682</v>
+        <v>88722</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8534,42 +8534,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471213</v>
+        <v>470929</v>
       </c>
       <c r="R67" t="n">
-        <v>7140791</v>
+        <v>7141002</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8593,22 +8588,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8623,15 +8608,127 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128157802</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Håagkat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>471213</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7140791</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8526,7 +8526,7 @@
         <v>128051879</v>
       </c>
       <c r="B67" t="n">
-        <v>88722</v>
+        <v>88734</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>128157802</v>
       </c>
       <c r="B68" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8526,7 +8526,7 @@
         <v>128051879</v>
       </c>
       <c r="B67" t="n">
-        <v>88734</v>
+        <v>88736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -7550,7 +7550,7 @@
         <v>126782070</v>
       </c>
       <c r="B59" t="n">
-        <v>56844</v>
+        <v>56840</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>126782095</v>
       </c>
       <c r="B60" t="n">
-        <v>56844</v>
+        <v>56840</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7809,10 +7809,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126782282</v>
+        <v>126783407</v>
       </c>
       <c r="B61" t="n">
-        <v>56844</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7820,16 +7820,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7837,24 +7837,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7863,13 +7849,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>470941</v>
+        <v>471028</v>
       </c>
       <c r="R61" t="n">
-        <v>7140824</v>
+        <v>7140823</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7898,7 +7884,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7908,12 +7894,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7940,48 +7926,67 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126781777</v>
+        <v>126782282</v>
       </c>
       <c r="B62" t="n">
-        <v>98468</v>
+        <v>56840</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470980</v>
+        <v>470941</v>
       </c>
       <c r="R62" t="n">
-        <v>7140865</v>
+        <v>7140824</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8021,6 +8026,11 @@
       <c r="AB62" t="inlineStr">
         <is>
           <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8047,47 +8057,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126782391</v>
+        <v>126786066</v>
       </c>
       <c r="B63" t="n">
-        <v>98364</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8096,13 +8102,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470927</v>
+        <v>470941</v>
       </c>
       <c r="R63" t="n">
-        <v>7140809</v>
+        <v>7140824</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8129,19 +8135,14 @@
           <t>2025-07-20</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-20</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:58</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Födosökande tretå i lämplig häckningsbiotop. Precis bredvid är en gran med färska samt äldre ringhack. dessutom finns flertalet födosökspår färska samt äldre och ringhackade granar med färska samt äldre ringhack. Tretå har observerats i området året runt i flera år.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8152,6 +8153,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8168,7 +8174,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126783407</v>
+        <v>126785249</v>
       </c>
       <c r="B64" t="n">
         <v>57672</v>
@@ -8196,10 +8202,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8208,10 +8218,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471028</v>
+        <v>470934</v>
       </c>
       <c r="R64" t="n">
-        <v>7140823</v>
+        <v>7140818</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8243,7 +8253,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8253,12 +8263,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
+          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8285,58 +8295,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126786066</v>
+        <v>126781777</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>98457</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>470941</v>
+        <v>470980</v>
       </c>
       <c r="R65" t="n">
-        <v>7140824</v>
+        <v>7140865</v>
       </c>
       <c r="S65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8363,14 +8363,19 @@
           <t>2025-07-20</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-20</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Födosökande tretå i lämplig häckningsbiotop. Precis bredvid är en gran med färska samt äldre ringhack. dessutom finns flertalet födosökspår färska samt äldre och ringhackade granar med färska samt äldre ringhack. Tretå har observerats i området året runt i flera år.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8381,11 +8386,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8402,42 +8402,47 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126785249</v>
+        <v>126782391</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>98353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8446,10 +8451,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470934</v>
+        <v>470927</v>
       </c>
       <c r="R66" t="n">
-        <v>7140818</v>
+        <v>7140809</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8481,7 +8486,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8491,12 +8496,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -8288,7 +8288,7 @@
         <v>126786066</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>57864</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95408907</v>
+        <v>119787378</v>
       </c>
       <c r="B2" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,52 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>620</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Håkafot 525, Strömsund, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471141.3904761148</v>
+        <v>470975</v>
       </c>
       <c r="R2" t="n">
-        <v>7140801.824951868</v>
+        <v>7140803</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,86 +757,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Rashid Kadhim, Jonny Daborg, Hugo Ström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93854703</v>
+        <v>119787342</v>
       </c>
       <c r="B3" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>620</v>
+        <v>445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Håkafot 525, Strömsund, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471142.3261687885</v>
+        <v>470975</v>
       </c>
       <c r="R3" t="n">
-        <v>7140809.172078269</v>
+        <v>7140803</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,33 +858,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonny Daborg</t>
+          <t>Rashid Kadhim, Jonny Daborg, Hugo Ström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95409053</v>
+        <v>93854686</v>
       </c>
       <c r="B4" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,7 +907,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -972,18 +915,22 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Håkafot 525, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471001.5130752933</v>
+        <v>471142</v>
       </c>
       <c r="R4" t="n">
-        <v>7140808.33802441</v>
+        <v>7140809</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1010,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116198155</v>
+        <v>95408888</v>
       </c>
       <c r="B5" t="n">
-        <v>90435</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,46 +1000,52 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>620</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>., Jmt</t>
+          <t>Håkafot 525, Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471198</v>
+        <v>471141</v>
       </c>
       <c r="R5" t="n">
-        <v>7140948</v>
+        <v>7140802</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,12 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,88 +1085,75 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Jonny Daborg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Jonny Daborg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118610117</v>
+        <v>95409050</v>
       </c>
       <c r="B6" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Håagkat (Håagkat), Jmt</t>
+          <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471181</v>
+        <v>471002</v>
       </c>
       <c r="R6" t="n">
-        <v>7140954</v>
+        <v>7140808</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,12 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,88 +1193,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jonny Daborg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jonny Daborg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118610965</v>
+        <v>118649741</v>
       </c>
       <c r="B7" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471000</v>
+        <v>471038</v>
       </c>
       <c r="R7" t="n">
-        <v>7140801</v>
+        <v>7140797</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,12 +1274,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,64 +1316,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118610548</v>
+        <v>118615387</v>
       </c>
       <c r="B8" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471004</v>
+        <v>471126</v>
       </c>
       <c r="R8" t="n">
-        <v>7140974</v>
+        <v>7140737</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1506,9 +1398,19 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1526,64 +1428,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118613050</v>
+        <v>118653585</v>
       </c>
       <c r="B9" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471123</v>
+        <v>471126</v>
       </c>
       <c r="R9" t="n">
-        <v>7140909</v>
+        <v>7140737</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1610,12 +1493,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,67 +1535,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118610401</v>
+        <v>118652356</v>
       </c>
       <c r="B10" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471080</v>
+        <v>471011</v>
       </c>
       <c r="R10" t="n">
-        <v>7140963</v>
+        <v>7140906</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1726,12 +1605,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,11 +1631,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1763,67 +1647,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118611103</v>
+        <v>118654317</v>
       </c>
       <c r="B11" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkafot (Håkafot), Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470955</v>
+        <v>471203</v>
       </c>
       <c r="R11" t="n">
-        <v>7140903</v>
+        <v>7140769</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1847,12 +1717,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosök Spillkråka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1879,64 +1764,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118609933</v>
+        <v>128157802</v>
       </c>
       <c r="B12" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håagkat (Håagkat), Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471229</v>
+        <v>471213</v>
       </c>
       <c r="R12" t="n">
-        <v>7140929</v>
+        <v>7140791</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1963,12 +1834,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,11 +1860,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2000,15 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118615387</v>
+        <v>122603006</v>
       </c>
       <c r="B13" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,37 +1887,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471126</v>
+        <v>470980</v>
       </c>
       <c r="R13" t="n">
-        <v>7140737</v>
+        <v>7140865</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2070,12 +1951,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,19 +1973,9 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2117,15 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118619895</v>
+        <v>126782340</v>
       </c>
       <c r="B14" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,16 +2004,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2151,19 +2022,9 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,13 +2033,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471080</v>
+        <v>470941</v>
       </c>
       <c r="R14" t="n">
-        <v>7140901</v>
+        <v>7140824</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2202,22 +2063,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,11 +2089,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2249,15 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118632946</v>
+        <v>126783407</v>
       </c>
       <c r="B15" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,16 +2116,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2282,19 +2133,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2303,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471124</v>
+        <v>471028</v>
       </c>
       <c r="R15" t="n">
-        <v>7140767</v>
+        <v>7140823</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2333,27 +2175,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
+          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,15 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118633149</v>
+        <v>126785249</v>
       </c>
       <c r="B16" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,16 +2233,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2418,14 +2255,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2434,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471126</v>
+        <v>470934</v>
       </c>
       <c r="R16" t="n">
-        <v>7140737</v>
+        <v>7140818</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2464,22 +2296,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,52 +2343,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118657609</v>
+        <v>118619895</v>
       </c>
       <c r="B17" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2560,13 +2393,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470892</v>
+        <v>471080</v>
       </c>
       <c r="R17" t="n">
-        <v>7140851</v>
+        <v>7140901</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2590,27 +2423,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor/rosetter.</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2621,6 +2449,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2637,15 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118654541</v>
+        <v>118632946</v>
       </c>
       <c r="B18" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,36 +2481,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2691,13 +2519,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471220</v>
+        <v>471124</v>
       </c>
       <c r="R18" t="n">
-        <v>7140873</v>
+        <v>7140767</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2726,7 +2554,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2736,7 +2564,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2763,52 +2596,47 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118656619</v>
+        <v>118633149</v>
       </c>
       <c r="B19" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2817,13 +2645,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471105</v>
+        <v>471126</v>
       </c>
       <c r="R19" t="n">
-        <v>7140950</v>
+        <v>7140737</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2847,22 +2675,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2889,32 +2717,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118656092</v>
+        <v>118653001</v>
       </c>
       <c r="B20" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2922,10 +2745,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2934,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471143</v>
+        <v>471105</v>
       </c>
       <c r="R20" t="n">
-        <v>7141012</v>
+        <v>7140803</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2964,22 +2796,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3006,32 +2838,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118652356</v>
+        <v>118658352</v>
       </c>
       <c r="B21" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3040,9 +2867,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3051,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471011</v>
+        <v>471000</v>
       </c>
       <c r="R21" t="n">
-        <v>7140906</v>
+        <v>7140830</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3081,22 +2918,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3123,15 +2960,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118653585</v>
+        <v>122603183</v>
       </c>
       <c r="B22" t="n">
-        <v>79609</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,34 +2971,53 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471126</v>
+        <v>471073</v>
       </c>
       <c r="R22" t="n">
-        <v>7140737</v>
+        <v>7140813</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3193,22 +3044,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3219,6 +3065,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3235,15 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118658808</v>
+        <v>126782059</v>
       </c>
       <c r="B23" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3251,21 +3097,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3273,14 +3119,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3289,10 +3140,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471124</v>
+        <v>470892</v>
       </c>
       <c r="R23" t="n">
-        <v>7140767</v>
+        <v>7140851</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3319,22 +3170,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3361,52 +3217,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118654949</v>
+        <v>126782095</v>
       </c>
       <c r="B24" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3415,13 +3271,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471177</v>
+        <v>470917</v>
       </c>
       <c r="R24" t="n">
-        <v>7140901</v>
+        <v>7140839</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3445,12 +3301,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3477,52 +3348,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118655376</v>
+        <v>126782120</v>
       </c>
       <c r="B25" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3531,13 +3402,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471154</v>
+        <v>470941</v>
       </c>
       <c r="R25" t="n">
-        <v>7140912</v>
+        <v>7140824</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3561,27 +3432,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 500 rosetter inom ca.9 kvm yta</t>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3608,53 +3479,62 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118649741</v>
+        <v>118655326</v>
       </c>
       <c r="B26" t="n">
-        <v>90524</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1205</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471038</v>
+        <v>471150</v>
       </c>
       <c r="R26" t="n">
-        <v>7140797</v>
+        <v>7140890</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3678,22 +3558,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3720,15 +3600,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118655326</v>
+        <v>118654475</v>
       </c>
       <c r="B27" t="n">
-        <v>57403</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3736,21 +3611,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3758,14 +3633,14 @@
           <t>3</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3774,13 +3649,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471150</v>
+        <v>471220</v>
       </c>
       <c r="R27" t="n">
-        <v>7140890</v>
+        <v>7140873</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3809,7 +3684,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3819,7 +3694,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3846,53 +3721,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118657198</v>
+        <v>118658808</v>
       </c>
       <c r="B28" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3901,13 +3770,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>470996</v>
+        <v>471124</v>
       </c>
       <c r="R28" t="n">
-        <v>7140928</v>
+        <v>7140767</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3936,7 +3805,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3946,12 +3815,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Järpe med ungar boplats vid vindfällen</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3978,52 +3842,47 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118656270</v>
+        <v>126266987</v>
       </c>
       <c r="B29" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4032,13 +3891,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471176</v>
+        <v>470927</v>
       </c>
       <c r="R29" t="n">
-        <v>7140877</v>
+        <v>7140793</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4062,27 +3921,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Va. 1 kvm med rosetter vissa delar mattbildande.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4109,50 +3963,59 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118649845</v>
+        <v>126267316</v>
       </c>
       <c r="B30" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471124</v>
+        <v>471000</v>
       </c>
       <c r="R30" t="n">
-        <v>7140767</v>
+        <v>7140801</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4179,22 +4042,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4221,52 +4084,47 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118656490</v>
+        <v>126782391</v>
       </c>
       <c r="B31" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4275,13 +4133,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471159</v>
+        <v>470927</v>
       </c>
       <c r="R31" t="n">
-        <v>7140899</v>
+        <v>7140809</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4305,27 +4163,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>15-20 kvm stor yta beväxt med bladeosetter många sjok mattbildande</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4352,52 +4205,47 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118655469</v>
+        <v>118610957</v>
       </c>
       <c r="B32" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ägg</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äggskal</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4406,13 +4254,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471147</v>
+        <v>471000</v>
       </c>
       <c r="R32" t="n">
-        <v>7140935</v>
+        <v>7140801</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4436,27 +4284,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4483,58 +4316,62 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118652300</v>
+        <v>118611103</v>
       </c>
       <c r="B33" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470932</v>
+        <v>470955</v>
       </c>
       <c r="R33" t="n">
-        <v>7140929</v>
+        <v>7140903</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4558,22 +4395,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4600,15 +4427,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118658516</v>
+        <v>118613050</v>
       </c>
       <c r="B34" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,17 +4457,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4654,13 +4476,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471011</v>
+        <v>471123</v>
       </c>
       <c r="R34" t="n">
-        <v>7140807</v>
+        <v>7140909</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4684,27 +4506,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4731,58 +4538,62 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118654317</v>
+        <v>118654949</v>
       </c>
       <c r="B35" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471203</v>
+        <v>471177</v>
       </c>
       <c r="R35" t="n">
-        <v>7140769</v>
+        <v>7140901</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4806,27 +4617,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Födosök Spillkråka</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4853,53 +4649,47 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118658352</v>
+        <v>118655215</v>
       </c>
       <c r="B36" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4908,10 +4698,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471000</v>
+        <v>471154</v>
       </c>
       <c r="R36" t="n">
-        <v>7140830</v>
+        <v>7140912</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4941,19 +4731,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4980,52 +4760,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118653001</v>
+        <v>118656206</v>
       </c>
       <c r="B37" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5034,10 +4804,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471105</v>
+        <v>471176</v>
       </c>
       <c r="R37" t="n">
-        <v>7140803</v>
+        <v>7140877</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5064,22 +4834,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5106,52 +4876,47 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118701375</v>
+        <v>118656399</v>
       </c>
       <c r="B38" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5160,10 +4925,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471115</v>
+        <v>471159</v>
       </c>
       <c r="R38" t="n">
-        <v>7140993</v>
+        <v>7140899</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5190,17 +4955,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 2 Järpekycklingar vid vindfälle med höna. Boplats häckning</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5227,53 +4997,62 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118745232</v>
+        <v>118657575</v>
       </c>
       <c r="B39" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>470948</v>
+        <v>470892</v>
       </c>
       <c r="R39" t="n">
-        <v>7141024</v>
+        <v>7140851</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5297,12 +5076,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5329,15 +5118,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119787342</v>
+        <v>118658516</v>
       </c>
       <c r="B40" t="n">
-        <v>86156</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5345,37 +5129,48 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>445</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470975</v>
+        <v>471011</v>
       </c>
       <c r="R40" t="n">
-        <v>7140803</v>
+        <v>7140807</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5402,12 +5197,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5416,75 +5226,80 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg, Hugo Ström</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119787378</v>
+        <v>126264186</v>
       </c>
       <c r="B41" t="n">
-        <v>86306</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>427</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>470975</v>
+        <v>470971</v>
       </c>
       <c r="R41" t="n">
-        <v>7140803</v>
+        <v>7140842</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5508,12 +5323,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5522,76 +5347,65 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg, Hugo Ström</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122603183</v>
+        <v>126273173</v>
       </c>
       <c r="B42" t="n">
-        <v>56680</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5600,13 +5414,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471073</v>
+        <v>470992</v>
       </c>
       <c r="R42" t="n">
-        <v>7140813</v>
+        <v>7140849</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5630,17 +5444,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5651,11 +5460,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5672,50 +5476,35 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122603006</v>
+        <v>126781777</v>
       </c>
       <c r="B43" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
@@ -5752,17 +5541,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5773,11 +5567,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5794,59 +5583,59 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123377514</v>
+        <v>126782585</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471066</v>
+        <v>470849</v>
       </c>
       <c r="R44" t="n">
-        <v>7141025</v>
+        <v>7140849</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5873,17 +5662,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5910,15 +5704,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123377834</v>
+        <v>128051879</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5926,42 +5715,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471007</v>
+        <v>470929</v>
       </c>
       <c r="R45" t="n">
-        <v>7141045</v>
+        <v>7141002</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5985,17 +5769,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6010,44 +5789,39 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123377276</v>
+        <v>115383522</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6055,26 +5829,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471094</v>
+        <v>471015</v>
       </c>
       <c r="R46" t="n">
-        <v>7141017</v>
+        <v>7141073</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -6101,17 +5866,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>Även observerat Spillkråka flygande flera ggr i veckan.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6122,48 +5887,48 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123377064</v>
+        <v>118652300</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6172,19 +5937,24 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471175</v>
+        <v>470932</v>
       </c>
       <c r="R47" t="n">
-        <v>7140991</v>
+        <v>7140929</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6208,17 +5978,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6245,10 +6020,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126267316</v>
+        <v>118656092</v>
       </c>
       <c r="B48" t="n">
-        <v>98278</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6256,36 +6031,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6294,13 +6060,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471000</v>
+        <v>471143</v>
       </c>
       <c r="R48" t="n">
-        <v>7140801</v>
+        <v>7141012</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6324,22 +6090,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6366,14 +6132,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126265620</v>
+        <v>123377834</v>
       </c>
       <c r="B49" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -6397,19 +6163,19 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470985</v>
+        <v>471007</v>
       </c>
       <c r="R49" t="n">
-        <v>7141047</v>
+        <v>7141045</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6436,22 +6202,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6478,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126266135</v>
+        <v>126264916</v>
       </c>
       <c r="B50" t="n">
-        <v>98382</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6489,36 +6250,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6527,10 +6279,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470925</v>
+        <v>470985</v>
       </c>
       <c r="R50" t="n">
-        <v>7141000</v>
+        <v>7141047</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6562,7 +6314,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6572,7 +6324,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6599,57 +6351,60 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126266486</v>
+        <v>111954389</v>
       </c>
       <c r="B51" t="n">
-        <v>98278</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470908</v>
+        <v>471015</v>
       </c>
       <c r="R51" t="n">
-        <v>7140946</v>
+        <v>7141073</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6673,22 +6428,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6703,71 +6448,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126273173</v>
+        <v>118745232</v>
       </c>
       <c r="B52" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>470992</v>
+        <v>470948</v>
       </c>
       <c r="R52" t="n">
-        <v>7140849</v>
+        <v>7141024</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6794,12 +6525,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6826,59 +6557,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126266225</v>
+        <v>123377064</v>
       </c>
       <c r="B53" t="n">
-        <v>98265</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>470925</v>
+        <v>471175</v>
       </c>
       <c r="R53" t="n">
-        <v>7141000</v>
+        <v>7140991</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6905,22 +6622,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6947,59 +6659,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126266106</v>
+        <v>123377276</v>
       </c>
       <c r="B54" t="n">
-        <v>98278</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>470925</v>
+        <v>471094</v>
       </c>
       <c r="R54" t="n">
-        <v>7141000</v>
+        <v>7141017</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -7026,22 +6733,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7068,54 +6770,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126266654</v>
+        <v>123377514</v>
       </c>
       <c r="B55" t="n">
-        <v>98278</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470901</v>
+        <v>471066</v>
       </c>
       <c r="R55" t="n">
-        <v>7140921</v>
+        <v>7141025</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7142,22 +6844,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7184,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126264186</v>
+        <v>118655469</v>
       </c>
       <c r="B56" t="n">
-        <v>98382</v>
+        <v>57132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7195,36 +6892,36 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äggskal</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7233,13 +6930,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470971</v>
+        <v>471147</v>
       </c>
       <c r="R56" t="n">
-        <v>7140842</v>
+        <v>7140935</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7263,22 +6960,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7305,10 +7007,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126266987</v>
+        <v>118657198</v>
       </c>
       <c r="B57" t="n">
-        <v>98278</v>
+        <v>57132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7316,36 +7018,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7354,13 +7057,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>470927</v>
+        <v>470996</v>
       </c>
       <c r="R57" t="n">
-        <v>7140793</v>
+        <v>7140928</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7384,22 +7087,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Järpe med ungar boplats vid vindfällen</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7426,10 +7134,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126264597</v>
+        <v>118701309</v>
       </c>
       <c r="B58" t="n">
-        <v>98382</v>
+        <v>57132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7437,36 +7145,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7475,13 +7184,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470938</v>
+        <v>471115</v>
       </c>
       <c r="R58" t="n">
-        <v>7141021</v>
+        <v>7140993</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7505,22 +7214,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Järpehöna med minst 2 kycklingar befinner sig vid vindfälle av gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7547,64 +7251,59 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126782070</v>
+        <v>118611615</v>
       </c>
       <c r="B59" t="n">
-        <v>56844</v>
+        <v>99035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>470892</v>
+        <v>470931</v>
       </c>
       <c r="R59" t="n">
-        <v>7140851</v>
+        <v>7140959</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7631,27 +7330,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7678,52 +7362,47 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126782095</v>
+        <v>126266051</v>
       </c>
       <c r="B60" t="n">
-        <v>56844</v>
+        <v>99035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7732,13 +7411,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>470917</v>
+        <v>470969</v>
       </c>
       <c r="R60" t="n">
-        <v>7140839</v>
+        <v>7140999</v>
       </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7762,27 +7441,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7809,52 +7483,47 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126782282</v>
+        <v>126266106</v>
       </c>
       <c r="B61" t="n">
-        <v>56844</v>
+        <v>99035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7863,13 +7532,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>470941</v>
+        <v>470925</v>
       </c>
       <c r="R61" t="n">
-        <v>7140824</v>
+        <v>7141000</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7893,27 +7562,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7940,10 +7604,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126781777</v>
+        <v>126266189</v>
       </c>
       <c r="B62" t="n">
-        <v>98468</v>
+        <v>99035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7951,37 +7615,51 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470980</v>
+        <v>470917</v>
       </c>
       <c r="R62" t="n">
-        <v>7140865</v>
+        <v>7140990</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8005,22 +7683,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8047,10 +7725,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126782391</v>
+        <v>126266486</v>
       </c>
       <c r="B63" t="n">
-        <v>98364</v>
+        <v>99035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8077,7 +7755,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8085,24 +7763,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470927</v>
+        <v>470908</v>
       </c>
       <c r="R63" t="n">
-        <v>7140809</v>
+        <v>7140946</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8126,22 +7799,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8168,38 +7841,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126783407</v>
+        <v>126266654</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>99035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8208,10 +7885,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471028</v>
+        <v>470901</v>
       </c>
       <c r="R64" t="n">
-        <v>7140823</v>
+        <v>7140921</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8238,27 +7915,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8285,43 +7957,47 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126786066</v>
+        <v>126266225</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>99022</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8330,13 +8006,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>470941</v>
+        <v>470925</v>
       </c>
       <c r="R65" t="n">
-        <v>7140824</v>
+        <v>7141000</v>
       </c>
       <c r="S65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8360,17 +8036,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Födosökande tretå i lämplig häckningsbiotop. Precis bredvid är en gran med färska samt äldre ringhack. dessutom finns flertalet födosökspår färska samt äldre och ringhackade granar med färska samt äldre ringhack. Tretå har observerats i området året runt i flera år.</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8381,11 +8062,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8402,54 +8078,59 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126785249</v>
+        <v>118608782</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470934</v>
+        <v>471181</v>
       </c>
       <c r="R66" t="n">
-        <v>7140818</v>
+        <v>7140954</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8476,27 +8157,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8523,48 +8189,62 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128051879</v>
+        <v>118609933</v>
       </c>
       <c r="B67" t="n">
-        <v>88736</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470929</v>
+        <v>471229</v>
       </c>
       <c r="R67" t="n">
-        <v>7141002</v>
+        <v>7140929</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8588,12 +8268,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8604,66 +8284,80 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Staaf, Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128157802</v>
+        <v>118610401</v>
       </c>
       <c r="B68" t="n">
-        <v>57686</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471213</v>
+        <v>471080</v>
       </c>
       <c r="R68" t="n">
-        <v>7140791</v>
+        <v>7140963</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8690,22 +8384,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8716,6 +8400,11 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8729,6 +8418,485 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>118610548</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Håkafot, Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>471004</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7140974</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>118656619</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>471105</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7140950</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126264597</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>470938</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7141021</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126266135</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>470925</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7141000</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787378</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119787342</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93854686</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95408888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95409050</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118649741</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128051879</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118615387</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118653585</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383522</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118652300</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1960,6 +2020,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118652356</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118654317</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118656092</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2296,6 +2371,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377834</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126264916</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2520,6 +2605,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128157802</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2629,6 +2719,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954389</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2726,6 +2821,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745232</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2843,6 +2943,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122603006</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2945,6 +3050,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377064</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3056,6 +3166,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377276</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3167,6 +3282,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377514</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3279,6 +3399,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126782340</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3396,6 +3521,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126783407</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3517,6 +3647,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126785249</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3644,6 +3779,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118619895</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3770,6 +3910,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118632946</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3891,6 +4036,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118633149</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4012,6 +4162,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118653001</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4138,6 +4293,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118655469</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4265,6 +4425,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118657198</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4387,6 +4552,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658352</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4504,6 +4674,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118701309</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4630,6 +4805,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122603183</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4761,6 +4941,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126782059</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4892,6 +5077,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126782095</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5023,6 +5213,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126782120</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5144,6 +5339,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118655326</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5255,6 +5455,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118611615</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5376,6 +5581,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118654475</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5497,6 +5707,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658808</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5618,6 +5833,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266051</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5739,6 +5959,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266106</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5860,6 +6085,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266189</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5976,6 +6206,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266486</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6092,6 +6327,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266654</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6213,6 +6453,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266987</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6334,6 +6579,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126267316</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6455,6 +6705,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126782391</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6576,6 +6831,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266225</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6687,6 +6947,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118608782</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6803,6 +7068,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118609933</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6919,6 +7189,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610401</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7035,6 +7310,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610548</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7146,6 +7426,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610957</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7257,6 +7542,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118611103</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7368,6 +7658,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118613050</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7479,6 +7774,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118654949</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7590,6 +7890,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118655215</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7706,6 +8011,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118656206</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7827,6 +8137,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118656399</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7948,6 +8263,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118656619</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8069,6 +8389,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118657575</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8195,6 +8520,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658516</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8316,6 +8646,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126264186</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8437,6 +8772,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126264597</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8558,6 +8898,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266135</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8669,6 +9014,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126273173</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8776,6 +9126,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126781777</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8897,8 +9252,86 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126782585</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ72"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1351,48 +1351,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128051879</v>
+        <v>136202511</v>
       </c>
       <c r="B8" t="n">
-        <v>89156</v>
+        <v>87548</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4412</v>
+        <v>3624</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470929</v>
+        <v>471019</v>
       </c>
       <c r="R8" t="n">
-        <v>7141002</v>
+        <v>7141064</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,12 +1412,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,31 +1428,40 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Staaf, Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128051879</t>
+          <t>https://artportalen.se/Sighting/136202511</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118615387</v>
+        <v>136202482</v>
       </c>
       <c r="B9" t="n">
-        <v>80432</v>
+        <v>87511</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,37 +1469,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>3739</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471126</v>
+        <v>471029</v>
       </c>
       <c r="R9" t="n">
-        <v>7140737</v>
+        <v>7141075</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1518,12 +1523,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,83 +1540,73 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118615387</t>
+          <t>https://artportalen.se/Sighting/136202482</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118653585</v>
+        <v>136202509</v>
       </c>
       <c r="B10" t="n">
-        <v>80467</v>
+        <v>87511</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>3739</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471126</v>
+        <v>471019</v>
       </c>
       <c r="R10" t="n">
-        <v>7140737</v>
+        <v>7141064</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,22 +1630,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,69 +1646,78 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118653585</t>
+          <t>https://artportalen.se/Sighting/136202509</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115383522</v>
+        <v>136202506</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>89277</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>4404</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471015</v>
+        <v>471081</v>
       </c>
       <c r="R11" t="n">
-        <v>7141073</v>
+        <v>7140813</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,17 +1741,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Även observerat Spillkråka flygande flera ggr i veckan.</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,75 +1758,74 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115383522</t>
+          <t>https://artportalen.se/Sighting/136202506</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118652300</v>
+        <v>128051879</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>89156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470932</v>
+        <v>470929</v>
       </c>
       <c r="R12" t="n">
-        <v>7140929</v>
+        <v>7141002</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,22 +1852,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,70 +1872,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118652300</t>
+          <t>https://artportalen.se/Sighting/128051879</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118652356</v>
+        <v>118615387</v>
       </c>
       <c r="B13" t="n">
-        <v>57950</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471011</v>
+        <v>471126</v>
       </c>
       <c r="R13" t="n">
-        <v>7140906</v>
+        <v>7140737</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,22 +1954,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,6 +1970,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2022,16 +2000,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118652356</t>
+          <t>https://artportalen.se/Sighting/118615387</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118654317</v>
+        <v>118653585</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,42 +2017,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471203</v>
+        <v>471126</v>
       </c>
       <c r="R14" t="n">
-        <v>7140769</v>
+        <v>7140737</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2114,11 +2087,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosök Spillkråka</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,13 +2112,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118654317</t>
+          <t>https://artportalen.se/Sighting/118653585</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118656092</v>
+        <v>115383522</v>
       </c>
       <c r="B15" t="n">
         <v>57950</v>
@@ -2179,24 +2147,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471143</v>
+        <v>471015</v>
       </c>
       <c r="R15" t="n">
-        <v>7141012</v>
+        <v>7141073</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2220,22 +2183,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Även observerat Spillkråka flygande flera ggr i veckan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,28 +2204,33 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656092</t>
+          <t>https://artportalen.se/Sighting/115383522</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123377834</v>
+        <v>118652300</v>
       </c>
       <c r="B16" t="n">
         <v>57950</v>
@@ -2303,17 +2266,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471007</v>
+        <v>470932</v>
       </c>
       <c r="R16" t="n">
-        <v>7141045</v>
+        <v>7140929</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2337,17 +2300,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,13 +2341,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377834</t>
+          <t>https://artportalen.se/Sighting/118652300</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126264916</v>
+        <v>118652356</v>
       </c>
       <c r="B17" t="n">
         <v>57950</v>
@@ -2410,7 +2378,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2419,13 +2387,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470985</v>
+        <v>471011</v>
       </c>
       <c r="R17" t="n">
-        <v>7141047</v>
+        <v>7140906</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2449,22 +2417,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,13 +2458,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126264916</t>
+          <t>https://artportalen.se/Sighting/118652356</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128157802</v>
+        <v>118654317</v>
       </c>
       <c r="B18" t="n">
         <v>57950</v>
@@ -2527,7 +2495,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2536,13 +2504,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471213</v>
+        <v>471203</v>
       </c>
       <c r="R18" t="n">
-        <v>7140791</v>
+        <v>7140769</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2566,22 +2534,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosök Spillkråka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,33 +2580,33 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128157802</t>
+          <t>https://artportalen.se/Sighting/118654317</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111954389</v>
+        <v>118656092</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2642,31 +2615,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471015</v>
+        <v>471143</v>
       </c>
       <c r="R19" t="n">
-        <v>7141073</v>
+        <v>7141012</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2690,12 +2656,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,44 +2686,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111954389</t>
+          <t>https://artportalen.se/Sighting/118656092</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118745232</v>
+        <v>123377834</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2756,19 +2732,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470948</v>
+        <v>471007</v>
       </c>
       <c r="R20" t="n">
-        <v>7141024</v>
+        <v>7141045</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2792,12 +2773,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,33 +2809,33 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118745232</t>
+          <t>https://artportalen.se/Sighting/123377834</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122603006</v>
+        <v>126264916</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2858,14 +2844,9 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2874,13 +2855,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470980</v>
+        <v>470985</v>
       </c>
       <c r="R21" t="n">
-        <v>7140865</v>
+        <v>7141047</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,17 +2885,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,11 +2911,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2945,33 +2926,33 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122603006</t>
+          <t>https://artportalen.se/Sighting/126264916</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123377064</v>
+        <v>128157802</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2980,16 +2961,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471175</v>
+        <v>471213</v>
       </c>
       <c r="R22" t="n">
-        <v>7140991</v>
+        <v>7140791</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3016,17 +3002,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,13 +3043,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377064</t>
+          <t>https://artportalen.se/Sighting/128157802</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123377276</v>
+        <v>111954389</v>
       </c>
       <c r="B23" t="n">
         <v>57953</v>
@@ -3086,26 +3077,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471094</v>
+        <v>471015</v>
       </c>
       <c r="R23" t="n">
-        <v>7141017</v>
+        <v>7141073</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3132,17 +3126,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3157,24 +3146,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377276</t>
+          <t>https://artportalen.se/Sighting/111954389</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123377514</v>
+        <v>118745232</v>
       </c>
       <c r="B24" t="n">
         <v>57953</v>
@@ -3202,29 +3191,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471066</v>
+        <v>470948</v>
       </c>
       <c r="R24" t="n">
-        <v>7141025</v>
+        <v>7141024</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3248,17 +3228,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,13 +3259,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377514</t>
+          <t>https://artportalen.se/Sighting/118745232</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126782340</v>
+        <v>122603006</v>
       </c>
       <c r="B25" t="n">
         <v>57953</v>
@@ -3319,9 +3294,14 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3330,13 +3310,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>470941</v>
+        <v>470980</v>
       </c>
       <c r="R25" t="n">
-        <v>7140824</v>
+        <v>7140865</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3360,22 +3340,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,6 +3361,11 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3401,13 +3381,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782340</t>
+          <t>https://artportalen.se/Sighting/122603006</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126783407</v>
+        <v>123377064</v>
       </c>
       <c r="B26" t="n">
         <v>57953</v>
@@ -3436,21 +3416,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471028</v>
+        <v>471175</v>
       </c>
       <c r="R26" t="n">
-        <v>7140823</v>
+        <v>7140991</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3477,27 +3452,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,13 +3488,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126783407</t>
+          <t>https://artportalen.se/Sighting/123377064</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126785249</v>
+        <v>123377276</v>
       </c>
       <c r="B27" t="n">
         <v>57953</v>
@@ -3569,14 +3534,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>470934</v>
+        <v>471094</v>
       </c>
       <c r="R27" t="n">
-        <v>7140818</v>
+        <v>7141017</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3603,27 +3568,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3649,33 +3604,33 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126785249</t>
+          <t>https://artportalen.se/Sighting/123377276</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118619895</v>
+        <v>123377514</v>
       </c>
       <c r="B28" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3683,35 +3638,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471080</v>
+        <v>471066</v>
       </c>
       <c r="R28" t="n">
-        <v>7140901</v>
+        <v>7141025</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,22 +3684,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3761,11 +3705,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3781,33 +3720,33 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118619895</t>
+          <t>https://artportalen.se/Sighting/123377514</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118632946</v>
+        <v>126782340</v>
       </c>
       <c r="B29" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3815,19 +3754,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3836,13 +3766,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471124</v>
+        <v>470941</v>
       </c>
       <c r="R29" t="n">
-        <v>7140767</v>
+        <v>7140824</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3866,27 +3796,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,33 +3837,33 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118632946</t>
+          <t>https://artportalen.se/Sighting/126782340</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118633149</v>
+        <v>126783407</v>
       </c>
       <c r="B30" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3946,19 +3871,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3967,10 +3883,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471126</v>
+        <v>471028</v>
       </c>
       <c r="R30" t="n">
-        <v>7140737</v>
+        <v>7140823</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3997,22 +3913,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4038,33 +3959,33 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118633149</t>
+          <t>https://artportalen.se/Sighting/126783407</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118653001</v>
+        <v>126785249</v>
       </c>
       <c r="B31" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4074,17 +3995,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>pulli</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4093,13 +4009,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471105</v>
+        <v>470934</v>
       </c>
       <c r="R31" t="n">
-        <v>7140803</v>
+        <v>7140818</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4123,22 +4039,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4164,13 +4085,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118653001</t>
+          <t>https://artportalen.se/Sighting/126785249</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118655469</v>
+        <v>118619895</v>
       </c>
       <c r="B32" t="n">
         <v>57132</v>
@@ -4198,19 +4119,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äggskal</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4219,13 +4141,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471147</v>
+        <v>471080</v>
       </c>
       <c r="R32" t="n">
-        <v>7140935</v>
+        <v>7140901</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4249,27 +4171,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4280,6 +4197,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4295,13 +4217,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118655469</t>
+          <t>https://artportalen.se/Sighting/118619895</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118657198</v>
+        <v>118632946</v>
       </c>
       <c r="B33" t="n">
         <v>57132</v>
@@ -4329,20 +4251,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4351,13 +4272,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470996</v>
+        <v>471124</v>
       </c>
       <c r="R33" t="n">
-        <v>7140928</v>
+        <v>7140767</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4381,27 +4302,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Järpe med ungar boplats vid vindfällen</t>
+          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4427,13 +4348,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118657198</t>
+          <t>https://artportalen.se/Sighting/118632946</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118658352</v>
+        <v>118633149</v>
       </c>
       <c r="B34" t="n">
         <v>57132</v>
@@ -4461,17 +4382,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>bo, ägg/ungar</t>
@@ -4483,13 +4403,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471000</v>
+        <v>471126</v>
       </c>
       <c r="R34" t="n">
-        <v>7140830</v>
+        <v>7140737</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4513,22 +4433,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4554,13 +4474,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118658352</t>
+          <t>https://artportalen.se/Sighting/118633149</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118701309</v>
+        <v>118653001</v>
       </c>
       <c r="B35" t="n">
         <v>57132</v>
@@ -4588,20 +4508,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>pulli</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4610,13 +4529,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471115</v>
+        <v>471105</v>
       </c>
       <c r="R35" t="n">
-        <v>7140993</v>
+        <v>7140803</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4640,17 +4559,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Järpehöna med minst 2 kycklingar befinner sig vid vindfälle av gran.</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4676,13 +4600,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118701309</t>
+          <t>https://artportalen.se/Sighting/118653001</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122603183</v>
+        <v>118655469</v>
       </c>
       <c r="B36" t="n">
         <v>57132</v>
@@ -4717,17 +4641,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äggskal</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4736,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471073</v>
+        <v>471147</v>
       </c>
       <c r="R36" t="n">
-        <v>7140813</v>
+        <v>7140935</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4766,17 +4685,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4787,11 +4716,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4807,13 +4731,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122603183</t>
+          <t>https://artportalen.se/Sighting/118655469</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126782059</v>
+        <v>118657198</v>
       </c>
       <c r="B37" t="n">
         <v>57132</v>
@@ -4841,11 +4765,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>adult</t>
@@ -4858,7 +4778,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4867,13 +4787,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>470892</v>
+        <v>470996</v>
       </c>
       <c r="R37" t="n">
-        <v>7140851</v>
+        <v>7140928</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4897,27 +4817,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>Järpe med ungar boplats vid vindfällen</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4943,13 +4863,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782059</t>
+          <t>https://artportalen.se/Sighting/118657198</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126782095</v>
+        <v>118658352</v>
       </c>
       <c r="B38" t="n">
         <v>57132</v>
@@ -4977,11 +4897,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>adult</t>
@@ -4994,7 +4910,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5003,13 +4919,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>470917</v>
+        <v>471000</v>
       </c>
       <c r="R38" t="n">
-        <v>7140839</v>
+        <v>7140830</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5033,27 +4949,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5079,13 +4990,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782095</t>
+          <t>https://artportalen.se/Sighting/118658352</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126782120</v>
+        <v>118701309</v>
       </c>
       <c r="B39" t="n">
         <v>57132</v>
@@ -5113,11 +5024,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>adult</t>
@@ -5130,7 +5037,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5139,13 +5046,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>470941</v>
+        <v>471115</v>
       </c>
       <c r="R39" t="n">
-        <v>7140824</v>
+        <v>7140993</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5169,27 +5076,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>Järpehöna med minst 2 kycklingar befinner sig vid vindfälle av gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5215,33 +5112,33 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782120</t>
+          <t>https://artportalen.se/Sighting/118701309</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118655326</v>
+        <v>122603183</v>
       </c>
       <c r="B40" t="n">
-        <v>58057</v>
+        <v>57132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5251,7 +5148,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5259,9 +5156,14 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5270,13 +5172,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471150</v>
+        <v>471073</v>
       </c>
       <c r="R40" t="n">
-        <v>7140890</v>
+        <v>7140813</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5300,22 +5202,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5326,6 +5223,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5341,16 +5243,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118655326</t>
+          <t>https://artportalen.se/Sighting/122603183</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118611615</v>
+        <v>126782059</v>
       </c>
       <c r="B41" t="n">
-        <v>99035</v>
+        <v>57132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5358,48 +5260,53 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>470931</v>
+        <v>470892</v>
       </c>
       <c r="R41" t="n">
-        <v>7140959</v>
+        <v>7140851</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5426,12 +5333,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5457,16 +5379,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611615</t>
+          <t>https://artportalen.se/Sighting/126782059</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118654475</v>
+        <v>126782095</v>
       </c>
       <c r="B42" t="n">
-        <v>99035</v>
+        <v>57132</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5474,36 +5396,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5512,10 +5439,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471220</v>
+        <v>470917</v>
       </c>
       <c r="R42" t="n">
-        <v>7140873</v>
+        <v>7140839</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -5542,22 +5469,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5583,16 +5515,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118654475</t>
+          <t>https://artportalen.se/Sighting/126782095</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118658808</v>
+        <v>126782120</v>
       </c>
       <c r="B43" t="n">
-        <v>99035</v>
+        <v>57132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5600,21 +5532,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5622,14 +5554,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5638,13 +5575,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471124</v>
+        <v>470941</v>
       </c>
       <c r="R43" t="n">
-        <v>7140767</v>
+        <v>7140824</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5668,22 +5605,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5709,53 +5651,53 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118658808</t>
+          <t>https://artportalen.se/Sighting/126782120</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126266051</v>
+        <v>118655326</v>
       </c>
       <c r="B44" t="n">
-        <v>99035</v>
+        <v>58057</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5764,13 +5706,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>470969</v>
+        <v>471150</v>
       </c>
       <c r="R44" t="n">
-        <v>7140999</v>
+        <v>7140890</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5794,22 +5736,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5835,13 +5777,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266051</t>
+          <t>https://artportalen.se/Sighting/118655326</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126266106</v>
+        <v>118611615</v>
       </c>
       <c r="B45" t="n">
         <v>99035</v>
@@ -5871,7 +5813,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5881,19 +5823,19 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>470925</v>
+        <v>470931</v>
       </c>
       <c r="R45" t="n">
-        <v>7141000</v>
+        <v>7140959</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5920,22 +5862,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5961,13 +5893,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266106</t>
+          <t>https://artportalen.se/Sighting/118611615</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126266189</v>
+        <v>118654475</v>
       </c>
       <c r="B46" t="n">
         <v>99035</v>
@@ -6002,12 +5934,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6016,13 +5948,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>470917</v>
+        <v>471220</v>
       </c>
       <c r="R46" t="n">
-        <v>7140990</v>
+        <v>7140873</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6046,22 +5978,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6087,13 +6019,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266189</t>
+          <t>https://artportalen.se/Sighting/118654475</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126266486</v>
+        <v>118658808</v>
       </c>
       <c r="B47" t="n">
         <v>99035</v>
@@ -6123,12 +6055,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6137,13 +6074,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>470908</v>
+        <v>471124</v>
       </c>
       <c r="R47" t="n">
-        <v>7140946</v>
+        <v>7140767</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6167,22 +6104,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6208,13 +6145,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266486</t>
+          <t>https://artportalen.se/Sighting/118658808</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126266654</v>
+        <v>126266051</v>
       </c>
       <c r="B48" t="n">
         <v>99035</v>
@@ -6244,7 +6181,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6252,16 +6189,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>470901</v>
+        <v>470969</v>
       </c>
       <c r="R48" t="n">
-        <v>7140921</v>
+        <v>7140999</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6293,7 +6235,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6303,7 +6245,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6329,13 +6271,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266654</t>
+          <t>https://artportalen.se/Sighting/126266051</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126266987</v>
+        <v>126266106</v>
       </c>
       <c r="B49" t="n">
         <v>99035</v>
@@ -6384,10 +6326,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470927</v>
+        <v>470925</v>
       </c>
       <c r="R49" t="n">
-        <v>7140793</v>
+        <v>7141000</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6419,7 +6361,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6429,7 +6371,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6455,13 +6397,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266987</t>
+          <t>https://artportalen.se/Sighting/126266106</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126267316</v>
+        <v>126266189</v>
       </c>
       <c r="B50" t="n">
         <v>99035</v>
@@ -6491,7 +6433,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6501,7 +6443,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6510,10 +6452,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>471000</v>
+        <v>470917</v>
       </c>
       <c r="R50" t="n">
-        <v>7140801</v>
+        <v>7140990</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6545,7 +6487,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6555,7 +6497,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6581,13 +6523,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126267316</t>
+          <t>https://artportalen.se/Sighting/126266189</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126782391</v>
+        <v>126266486</v>
       </c>
       <c r="B51" t="n">
         <v>99035</v>
@@ -6617,7 +6559,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6625,24 +6567,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470927</v>
+        <v>470908</v>
       </c>
       <c r="R51" t="n">
-        <v>7140809</v>
+        <v>7140946</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6666,22 +6603,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6707,16 +6644,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782391</t>
+          <t>https://artportalen.se/Sighting/126266486</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126266225</v>
+        <v>126266654</v>
       </c>
       <c r="B52" t="n">
-        <v>99022</v>
+        <v>99035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6724,26 +6661,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6751,21 +6688,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>470925</v>
+        <v>470901</v>
       </c>
       <c r="R52" t="n">
-        <v>7141000</v>
+        <v>7140921</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6797,7 +6729,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6807,7 +6739,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6833,65 +6765,65 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266225</t>
+          <t>https://artportalen.se/Sighting/126266654</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118608782</v>
+        <v>126266987</v>
       </c>
       <c r="B53" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471181</v>
+        <v>470927</v>
       </c>
       <c r="R53" t="n">
-        <v>7140954</v>
+        <v>7140793</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6918,12 +6850,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6949,43 +6891,43 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608782</t>
+          <t>https://artportalen.se/Sighting/126266987</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118609933</v>
+        <v>126267316</v>
       </c>
       <c r="B54" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6995,19 +6937,19 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471229</v>
+        <v>471000</v>
       </c>
       <c r="R54" t="n">
-        <v>7140929</v>
+        <v>7140801</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -7034,12 +6976,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7050,11 +7002,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7070,43 +7017,43 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118609933</t>
+          <t>https://artportalen.se/Sighting/126267316</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118610401</v>
+        <v>126782391</v>
       </c>
       <c r="B55" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7116,19 +7063,19 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>471080</v>
+        <v>470927</v>
       </c>
       <c r="R55" t="n">
-        <v>7140963</v>
+        <v>7140809</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7155,12 +7102,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7171,11 +7128,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7191,43 +7143,43 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610401</t>
+          <t>https://artportalen.se/Sighting/126782391</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118610548</v>
+        <v>126266225</v>
       </c>
       <c r="B56" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7237,19 +7189,19 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>471004</v>
+        <v>470925</v>
       </c>
       <c r="R56" t="n">
-        <v>7140974</v>
+        <v>7141000</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7276,12 +7228,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7292,11 +7254,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7312,13 +7269,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610548</t>
+          <t>https://artportalen.se/Sighting/126266225</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118610957</v>
+        <v>118608782</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -7348,29 +7305,29 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471000</v>
+        <v>471181</v>
       </c>
       <c r="R57" t="n">
-        <v>7140801</v>
+        <v>7140954</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7428,13 +7385,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610957</t>
+          <t>https://artportalen.se/Sighting/118608782</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118611103</v>
+        <v>118609933</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -7464,7 +7421,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7479,14 +7436,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470955</v>
+        <v>471229</v>
       </c>
       <c r="R58" t="n">
-        <v>7140903</v>
+        <v>7140929</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7530,6 +7487,11 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
@@ -7544,13 +7506,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611103</t>
+          <t>https://artportalen.se/Sighting/118609933</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118613050</v>
+        <v>118610401</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7580,7 +7542,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7590,19 +7552,19 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>471123</v>
+        <v>471080</v>
       </c>
       <c r="R59" t="n">
-        <v>7140909</v>
+        <v>7140963</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7646,6 +7608,11 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7660,13 +7627,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118613050</t>
+          <t>https://artportalen.se/Sighting/118610401</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118654949</v>
+        <v>118610548</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7696,29 +7663,29 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>471177</v>
+        <v>471004</v>
       </c>
       <c r="R60" t="n">
-        <v>7140901</v>
+        <v>7140974</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7745,12 +7712,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7761,6 +7728,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7776,13 +7748,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118654949</t>
+          <t>https://artportalen.se/Sighting/118610548</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118655215</v>
+        <v>118610957</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7812,17 +7784,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7831,13 +7803,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471154</v>
+        <v>471000</v>
       </c>
       <c r="R61" t="n">
-        <v>7140912</v>
+        <v>7140801</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7861,12 +7833,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7892,13 +7864,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118655215</t>
+          <t>https://artportalen.se/Sighting/118610957</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118656206</v>
+        <v>118611103</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7928,7 +7900,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7936,19 +7908,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471176</v>
+        <v>470955</v>
       </c>
       <c r="R62" t="n">
-        <v>7140877</v>
+        <v>7140903</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7972,22 +7949,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8013,13 +7980,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656206</t>
+          <t>https://artportalen.se/Sighting/118611103</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118656399</v>
+        <v>118613050</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -8049,12 +8016,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8068,13 +8035,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471159</v>
+        <v>471123</v>
       </c>
       <c r="R63" t="n">
-        <v>7140899</v>
+        <v>7140909</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8098,22 +8065,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8139,13 +8096,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656399</t>
+          <t>https://artportalen.se/Sighting/118613050</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118656619</v>
+        <v>118654949</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -8175,7 +8132,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8194,13 +8151,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471105</v>
+        <v>471177</v>
       </c>
       <c r="R64" t="n">
-        <v>7140950</v>
+        <v>7140901</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8227,19 +8184,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8265,13 +8212,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656619</t>
+          <t>https://artportalen.se/Sighting/118654949</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118657575</v>
+        <v>118655215</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -8301,12 +8248,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8320,13 +8267,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>470892</v>
+        <v>471154</v>
       </c>
       <c r="R65" t="n">
-        <v>7140851</v>
+        <v>7140912</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8353,19 +8300,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8391,13 +8328,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118657575</t>
+          <t>https://artportalen.se/Sighting/118655215</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118658516</v>
+        <v>118656206</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -8427,17 +8364,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8446,10 +8378,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471011</v>
+        <v>471176</v>
       </c>
       <c r="R66" t="n">
-        <v>7140807</v>
+        <v>7140877</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8481,7 +8413,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8491,12 +8423,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8522,48 +8449,48 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118658516</t>
+          <t>https://artportalen.se/Sighting/118656206</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126264186</v>
+        <v>118656399</v>
       </c>
       <c r="B67" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8577,13 +8504,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470971</v>
+        <v>471159</v>
       </c>
       <c r="R67" t="n">
-        <v>7140842</v>
+        <v>7140899</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8607,22 +8534,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8648,48 +8575,48 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126264186</t>
+          <t>https://artportalen.se/Sighting/118656399</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126264597</v>
+        <v>118656619</v>
       </c>
       <c r="B68" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8703,13 +8630,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>470938</v>
+        <v>471105</v>
       </c>
       <c r="R68" t="n">
-        <v>7141021</v>
+        <v>7140950</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8733,22 +8660,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8774,48 +8701,48 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126264597</t>
+          <t>https://artportalen.se/Sighting/118656619</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126266135</v>
+        <v>118657575</v>
       </c>
       <c r="B69" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8829,10 +8756,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470925</v>
+        <v>470892</v>
       </c>
       <c r="R69" t="n">
-        <v>7141000</v>
+        <v>7140851</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8859,22 +8786,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8900,53 +8827,53 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266135</t>
+          <t>https://artportalen.se/Sighting/118657575</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126273173</v>
+        <v>118658516</v>
       </c>
       <c r="B70" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8955,13 +8882,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>470992</v>
+        <v>471011</v>
       </c>
       <c r="R70" t="n">
-        <v>7140849</v>
+        <v>7140807</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8985,12 +8912,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9016,51 +8958,56 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126273173</t>
+          <t>https://artportalen.se/Sighting/118658516</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126781777</v>
+        <v>136196782</v>
       </c>
       <c r="B71" t="n">
-        <v>99140</v>
+        <v>99294</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470980</v>
+        <v>471038</v>
       </c>
       <c r="R71" t="n">
-        <v>7140865</v>
+        <v>7140811</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9087,22 +9034,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9117,24 +9064,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126781777</t>
+          <t>https://artportalen.se/Sighting/136196782</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126782585</v>
+        <v>126264186</v>
       </c>
       <c r="B72" t="n">
         <v>99140</v>
@@ -9164,7 +9111,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9174,7 +9121,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9183,10 +9130,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470849</v>
+        <v>470971</v>
       </c>
       <c r="R72" t="n">
-        <v>7140849</v>
+        <v>7140842</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -9213,22 +9160,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9254,7 +9201,720 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/126264186</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126264597</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>470938</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7141021</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126264597</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126266135</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>470925</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7141000</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266135</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126273173</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>470992</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7140849</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126273173</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126781777</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>470980</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7140865</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126781777</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126782585</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>470849</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7140849</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126782585</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136202502</v>
+      </c>
+      <c r="B78" t="n">
+        <v>93386</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6331649</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Phellodon dititomentosus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Svantesson</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>471081</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7140813</v>
+      </c>
+      <c r="S78" t="n">
+        <v>71</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136202502</t>
         </is>
       </c>
     </row>
@@ -9331,6 +9991,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ78"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1239,48 +1239,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118649741</v>
+        <v>136195675</v>
       </c>
       <c r="B7" t="n">
-        <v>91920</v>
+        <v>91598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>900</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471038</v>
+        <v>470996</v>
       </c>
       <c r="R7" t="n">
-        <v>7140797</v>
+        <v>7141053</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,22 +1307,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,53 +1331,58 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118649741</t>
+          <t>https://artportalen.se/Sighting/136195675</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136202511</v>
+        <v>136195674</v>
       </c>
       <c r="B8" t="n">
-        <v>87548</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3624</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1382,13 +1390,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471019</v>
+        <v>470994</v>
       </c>
       <c r="R8" t="n">
-        <v>7141064</v>
+        <v>7140815</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,11 +1423,21 @@
           <t>2026-08-28</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1428,78 +1446,69 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202511</t>
+          <t>https://artportalen.se/Sighting/136195674</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136202482</v>
+        <v>118649741</v>
       </c>
       <c r="B9" t="n">
-        <v>87511</v>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3739</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471029</v>
+        <v>471038</v>
       </c>
       <c r="R9" t="n">
-        <v>7141075</v>
+        <v>7140797</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,12 +1532,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,59 +1559,50 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202482</t>
+          <t>https://artportalen.se/Sighting/118649741</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136202509</v>
+        <v>136202511</v>
       </c>
       <c r="B10" t="n">
-        <v>87511</v>
+        <v>87549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3739</v>
+        <v>3624</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Quél.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1606,7 +1616,7 @@
         <v>7141064</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,16 +1680,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202509</t>
+          <t>https://artportalen.se/Sighting/136202511</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136202506</v>
+        <v>136202482</v>
       </c>
       <c r="B11" t="n">
-        <v>89277</v>
+        <v>87512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,21 +1697,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4404</v>
+        <v>3739</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sotvaxskivling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrophorus camarophyllus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,13 +1721,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471081</v>
+        <v>471029</v>
       </c>
       <c r="R11" t="n">
-        <v>7140813</v>
+        <v>7141075</v>
       </c>
       <c r="S11" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,11 +1768,7 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1781,16 +1787,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202506</t>
+          <t>https://artportalen.se/Sighting/136202482</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128051879</v>
+        <v>136202509</v>
       </c>
       <c r="B12" t="n">
-        <v>89156</v>
+        <v>87512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,37 +1804,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4412</v>
+        <v>3739</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470929</v>
+        <v>471019</v>
       </c>
       <c r="R12" t="n">
-        <v>7141002</v>
+        <v>7141064</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,12 +1858,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,31 +1874,40 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Staaf, Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128051879</t>
+          <t>https://artportalen.se/Sighting/136202509</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118615387</v>
+        <v>136202506</v>
       </c>
       <c r="B13" t="n">
-        <v>80432</v>
+        <v>89278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,37 +1915,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>4404</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471126</v>
+        <v>471081</v>
       </c>
       <c r="R13" t="n">
-        <v>7140737</v>
+        <v>7140813</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1954,12 +1969,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,67 +1986,61 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118615387</t>
+          <t>https://artportalen.se/Sighting/136202506</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118653585</v>
+        <v>128051879</v>
       </c>
       <c r="B14" t="n">
-        <v>80467</v>
+        <v>89156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>4412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,13 +2050,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471126</v>
+        <v>470929</v>
       </c>
       <c r="R14" t="n">
-        <v>7140737</v>
+        <v>7141002</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,22 +2080,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,27 +2100,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118653585</t>
+          <t>https://artportalen.se/Sighting/128051879</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115383522</v>
+        <v>136200761</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>92029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,37 +2128,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471015</v>
+        <v>470985</v>
       </c>
       <c r="R15" t="n">
-        <v>7141073</v>
+        <v>7141033</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,17 +2185,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Även observerat Spillkråka flygande flera ggr i veckan.</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,81 +2199,72 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115383522</t>
+          <t>https://artportalen.se/Sighting/136200761</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118652300</v>
+        <v>118615387</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470932</v>
+        <v>471126</v>
       </c>
       <c r="R16" t="n">
-        <v>7140929</v>
+        <v>7140737</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,22 +2288,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,6 +2304,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2341,16 +2334,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118652300</t>
+          <t>https://artportalen.se/Sighting/118615387</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118652356</v>
+        <v>118653585</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>80467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,42 +2351,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471011</v>
+        <v>471126</v>
       </c>
       <c r="R17" t="n">
-        <v>7140906</v>
+        <v>7140737</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2422,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2432,7 +2420,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,13 +2446,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118652356</t>
+          <t>https://artportalen.se/Sighting/118653585</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118654317</v>
+        <v>115383522</v>
       </c>
       <c r="B18" t="n">
         <v>57950</v>
@@ -2493,24 +2481,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471203</v>
+        <v>471015</v>
       </c>
       <c r="R18" t="n">
-        <v>7140769</v>
+        <v>7141073</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2534,27 +2517,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Födosök Spillkråka</t>
+          <t>Även observerat Spillkråka flygande flera ggr i veckan.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,28 +2538,33 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118654317</t>
+          <t>https://artportalen.se/Sighting/115383522</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118656092</v>
+        <v>118652300</v>
       </c>
       <c r="B19" t="n">
         <v>57950</v>
@@ -2626,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471143</v>
+        <v>470932</v>
       </c>
       <c r="R19" t="n">
-        <v>7141012</v>
+        <v>7140929</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,22 +2634,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2697,13 +2675,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656092</t>
+          <t>https://artportalen.se/Sighting/118652300</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123377834</v>
+        <v>118652356</v>
       </c>
       <c r="B20" t="n">
         <v>57950</v>
@@ -2739,17 +2717,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471007</v>
+        <v>471011</v>
       </c>
       <c r="R20" t="n">
-        <v>7141045</v>
+        <v>7140906</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2773,17 +2751,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,13 +2792,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377834</t>
+          <t>https://artportalen.se/Sighting/118652356</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126264916</v>
+        <v>118654317</v>
       </c>
       <c r="B21" t="n">
         <v>57950</v>
@@ -2846,22 +2829,22 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470985</v>
+        <v>471203</v>
       </c>
       <c r="R21" t="n">
-        <v>7141047</v>
+        <v>7140769</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,22 +2868,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosök Spillkråka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,13 +2914,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126264916</t>
+          <t>https://artportalen.se/Sighting/118654317</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128157802</v>
+        <v>118656092</v>
       </c>
       <c r="B22" t="n">
         <v>57950</v>
@@ -2963,22 +2951,22 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471213</v>
+        <v>471143</v>
       </c>
       <c r="R22" t="n">
-        <v>7140791</v>
+        <v>7141012</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3002,22 +2990,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3043,33 +3031,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128157802</t>
+          <t>https://artportalen.se/Sighting/118656092</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111954389</v>
+        <v>123377834</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3078,28 +3066,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471015</v>
+        <v>471007</v>
       </c>
       <c r="R23" t="n">
-        <v>7141073</v>
+        <v>7141045</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3126,12 +3107,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3146,44 +3132,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111954389</t>
+          <t>https://artportalen.se/Sighting/123377834</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118745232</v>
+        <v>126264916</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3192,19 +3178,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470948</v>
+        <v>470985</v>
       </c>
       <c r="R24" t="n">
-        <v>7141024</v>
+        <v>7141047</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3228,12 +3219,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,33 +3260,33 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118745232</t>
+          <t>https://artportalen.se/Sighting/126264916</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122603006</v>
+        <v>128157802</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3294,29 +3295,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>470980</v>
+        <v>471213</v>
       </c>
       <c r="R25" t="n">
-        <v>7140865</v>
+        <v>7140791</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3340,17 +3336,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3361,11 +3362,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3381,13 +3377,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122603006</t>
+          <t>https://artportalen.se/Sighting/128157802</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123377064</v>
+        <v>111954389</v>
       </c>
       <c r="B26" t="n">
         <v>57953</v>
@@ -3416,16 +3412,28 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471175</v>
+        <v>471015</v>
       </c>
       <c r="R26" t="n">
-        <v>7140991</v>
+        <v>7141073</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3452,17 +3460,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3477,24 +3480,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377064</t>
+          <t>https://artportalen.se/Sighting/111954389</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123377276</v>
+        <v>118745232</v>
       </c>
       <c r="B27" t="n">
         <v>57953</v>
@@ -3522,29 +3525,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471094</v>
+        <v>470948</v>
       </c>
       <c r="R27" t="n">
-        <v>7141017</v>
+        <v>7141024</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,17 +3562,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,13 +3593,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377276</t>
+          <t>https://artportalen.se/Sighting/118745232</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123377514</v>
+        <v>122603006</v>
       </c>
       <c r="B28" t="n">
         <v>57953</v>
@@ -3638,29 +3627,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471066</v>
+        <v>470980</v>
       </c>
       <c r="R28" t="n">
-        <v>7141025</v>
+        <v>7140865</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,17 +3674,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3705,6 +3695,11 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3720,13 +3715,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377514</t>
+          <t>https://artportalen.se/Sighting/122603006</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126782340</v>
+        <v>123377064</v>
       </c>
       <c r="B29" t="n">
         <v>57953</v>
@@ -3755,24 +3750,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>470941</v>
+        <v>471175</v>
       </c>
       <c r="R29" t="n">
-        <v>7140824</v>
+        <v>7140991</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3796,22 +3786,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3837,13 +3822,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782340</t>
+          <t>https://artportalen.se/Sighting/123377064</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126783407</v>
+        <v>123377276</v>
       </c>
       <c r="B30" t="n">
         <v>57953</v>
@@ -3871,22 +3856,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471028</v>
+        <v>471094</v>
       </c>
       <c r="R30" t="n">
-        <v>7140823</v>
+        <v>7141017</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3913,27 +3902,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3959,13 +3938,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126783407</t>
+          <t>https://artportalen.se/Sighting/123377276</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126785249</v>
+        <v>123377514</v>
       </c>
       <c r="B31" t="n">
         <v>57953</v>
@@ -4005,14 +3984,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>470934</v>
+        <v>471066</v>
       </c>
       <c r="R31" t="n">
-        <v>7140818</v>
+        <v>7141025</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4039,27 +4018,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4085,33 +4054,33 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126785249</t>
+          <t>https://artportalen.se/Sighting/123377514</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118619895</v>
+        <v>126782340</v>
       </c>
       <c r="B32" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4120,19 +4089,9 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4141,13 +4100,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471080</v>
+        <v>470941</v>
       </c>
       <c r="R32" t="n">
-        <v>7140901</v>
+        <v>7140824</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4171,22 +4130,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4197,11 +4156,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4217,33 +4171,33 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118619895</t>
+          <t>https://artportalen.se/Sighting/126782340</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118632946</v>
+        <v>126783407</v>
       </c>
       <c r="B33" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4251,19 +4205,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4272,10 +4217,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471124</v>
+        <v>471028</v>
       </c>
       <c r="R33" t="n">
-        <v>7140767</v>
+        <v>7140823</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4302,27 +4247,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
+          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4348,33 +4293,33 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118632946</t>
+          <t>https://artportalen.se/Sighting/126783407</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118633149</v>
+        <v>126785249</v>
       </c>
       <c r="B34" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4387,14 +4332,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4403,10 +4343,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471126</v>
+        <v>470934</v>
       </c>
       <c r="R34" t="n">
-        <v>7140737</v>
+        <v>7140818</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4433,22 +4373,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4474,13 +4419,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118633149</t>
+          <t>https://artportalen.se/Sighting/126785249</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118653001</v>
+        <v>118619895</v>
       </c>
       <c r="B35" t="n">
         <v>57132</v>
@@ -4508,19 +4453,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>pulli</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4529,10 +4475,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471105</v>
+        <v>471080</v>
       </c>
       <c r="R35" t="n">
-        <v>7140803</v>
+        <v>7140901</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4559,22 +4505,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4585,6 +4531,11 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4600,13 +4551,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118653001</t>
+          <t>https://artportalen.se/Sighting/118619895</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118655469</v>
+        <v>118632946</v>
       </c>
       <c r="B36" t="n">
         <v>57132</v>
@@ -4636,7 +4587,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4646,7 +4597,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äggskal</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4655,13 +4606,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471147</v>
+        <v>471124</v>
       </c>
       <c r="R36" t="n">
-        <v>7140935</v>
+        <v>7140767</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4685,27 +4636,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
+          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4731,13 +4682,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118655469</t>
+          <t>https://artportalen.se/Sighting/118632946</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118657198</v>
+        <v>118633149</v>
       </c>
       <c r="B37" t="n">
         <v>57132</v>
@@ -4765,17 +4716,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>bo, ägg/ungar</t>
@@ -4787,13 +4737,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>470996</v>
+        <v>471126</v>
       </c>
       <c r="R37" t="n">
-        <v>7140928</v>
+        <v>7140737</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4817,27 +4767,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Järpe med ungar boplats vid vindfällen</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4863,13 +4808,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118657198</t>
+          <t>https://artportalen.se/Sighting/118633149</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118658352</v>
+        <v>118653001</v>
       </c>
       <c r="B38" t="n">
         <v>57132</v>
@@ -4897,20 +4842,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>pulli</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4919,13 +4863,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471000</v>
+        <v>471105</v>
       </c>
       <c r="R38" t="n">
-        <v>7140830</v>
+        <v>7140803</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4949,22 +4893,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4990,13 +4934,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118658352</t>
+          <t>https://artportalen.se/Sighting/118653001</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118701309</v>
+        <v>118655469</v>
       </c>
       <c r="B39" t="n">
         <v>57132</v>
@@ -5024,20 +4968,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>äggskal</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5046,13 +4989,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471115</v>
+        <v>471147</v>
       </c>
       <c r="R39" t="n">
-        <v>7140993</v>
+        <v>7140935</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5076,17 +5019,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Järpehöna med minst 2 kycklingar befinner sig vid vindfälle av gran.</t>
+          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5112,13 +5065,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118701309</t>
+          <t>https://artportalen.se/Sighting/118655469</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122603183</v>
+        <v>118657198</v>
       </c>
       <c r="B40" t="n">
         <v>57132</v>
@@ -5146,11 +5099,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>adult</t>
@@ -5161,9 +5110,9 @@
           <t>hona</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5172,13 +5121,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471073</v>
+        <v>470996</v>
       </c>
       <c r="R40" t="n">
-        <v>7140813</v>
+        <v>7140928</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5202,17 +5151,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>Järpe med ungar boplats vid vindfällen</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5223,11 +5182,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5243,13 +5197,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122603183</t>
+          <t>https://artportalen.se/Sighting/118657198</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126782059</v>
+        <v>118658352</v>
       </c>
       <c r="B41" t="n">
         <v>57132</v>
@@ -5277,11 +5231,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>adult</t>
@@ -5294,7 +5244,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5303,13 +5253,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>470892</v>
+        <v>471000</v>
       </c>
       <c r="R41" t="n">
-        <v>7140851</v>
+        <v>7140830</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5333,27 +5283,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5379,13 +5324,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782059</t>
+          <t>https://artportalen.se/Sighting/118658352</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126782095</v>
+        <v>118701309</v>
       </c>
       <c r="B42" t="n">
         <v>57132</v>
@@ -5413,11 +5358,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>adult</t>
@@ -5430,7 +5371,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5439,13 +5380,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>470917</v>
+        <v>471115</v>
       </c>
       <c r="R42" t="n">
-        <v>7140839</v>
+        <v>7140993</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5469,27 +5410,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>Järpehöna med minst 2 kycklingar befinner sig vid vindfälle av gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5515,13 +5446,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782095</t>
+          <t>https://artportalen.se/Sighting/118701309</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126782120</v>
+        <v>122603183</v>
       </c>
       <c r="B43" t="n">
         <v>57132</v>
@@ -5564,9 +5495,9 @@
           <t>hona</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5575,13 +5506,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>470941</v>
+        <v>471073</v>
       </c>
       <c r="R43" t="n">
-        <v>7140824</v>
+        <v>7140813</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5605,27 +5536,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5636,6 +5557,11 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5651,33 +5577,33 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782120</t>
+          <t>https://artportalen.se/Sighting/122603183</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118655326</v>
+        <v>126782059</v>
       </c>
       <c r="B44" t="n">
-        <v>58057</v>
+        <v>57132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5687,7 +5613,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5695,9 +5621,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5706,13 +5637,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471150</v>
+        <v>470892</v>
       </c>
       <c r="R44" t="n">
-        <v>7140890</v>
+        <v>7140851</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5736,22 +5667,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5777,16 +5713,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118655326</t>
+          <t>https://artportalen.se/Sighting/126782059</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118611615</v>
+        <v>126782095</v>
       </c>
       <c r="B45" t="n">
-        <v>99035</v>
+        <v>57132</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5794,51 +5730,56 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>470931</v>
+        <v>470917</v>
       </c>
       <c r="R45" t="n">
-        <v>7140959</v>
+        <v>7140839</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5862,12 +5803,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5893,16 +5849,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611615</t>
+          <t>https://artportalen.se/Sighting/126782095</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118654475</v>
+        <v>126782120</v>
       </c>
       <c r="B46" t="n">
-        <v>99035</v>
+        <v>57132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5910,36 +5866,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5948,10 +5909,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471220</v>
+        <v>470941</v>
       </c>
       <c r="R46" t="n">
-        <v>7140873</v>
+        <v>7140824</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5978,22 +5939,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6019,53 +5985,53 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118654475</t>
+          <t>https://artportalen.se/Sighting/126782120</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118658808</v>
+        <v>118655326</v>
       </c>
       <c r="B47" t="n">
-        <v>99035</v>
+        <v>58057</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6074,13 +6040,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471124</v>
+        <v>471150</v>
       </c>
       <c r="R47" t="n">
-        <v>7140767</v>
+        <v>7140890</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6109,7 +6075,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6119,7 +6085,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6145,13 +6111,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118658808</t>
+          <t>https://artportalen.se/Sighting/118655326</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126266051</v>
+        <v>118611615</v>
       </c>
       <c r="B48" t="n">
         <v>99035</v>
@@ -6181,7 +6147,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6191,19 +6157,19 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>470969</v>
+        <v>470931</v>
       </c>
       <c r="R48" t="n">
-        <v>7140999</v>
+        <v>7140959</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6230,22 +6196,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6271,13 +6227,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266051</t>
+          <t>https://artportalen.se/Sighting/118611615</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126266106</v>
+        <v>118654475</v>
       </c>
       <c r="B49" t="n">
         <v>99035</v>
@@ -6307,17 +6263,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6326,13 +6282,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470925</v>
+        <v>471220</v>
       </c>
       <c r="R49" t="n">
-        <v>7141000</v>
+        <v>7140873</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6356,22 +6312,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6397,13 +6353,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266106</t>
+          <t>https://artportalen.se/Sighting/118654475</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126266189</v>
+        <v>118658808</v>
       </c>
       <c r="B50" t="n">
         <v>99035</v>
@@ -6433,17 +6389,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6452,10 +6408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470917</v>
+        <v>471124</v>
       </c>
       <c r="R50" t="n">
-        <v>7140990</v>
+        <v>7140767</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6482,22 +6438,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6523,13 +6479,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266189</t>
+          <t>https://artportalen.se/Sighting/118658808</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126266486</v>
+        <v>126266051</v>
       </c>
       <c r="B51" t="n">
         <v>99035</v>
@@ -6559,7 +6515,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6567,19 +6523,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470908</v>
+        <v>470969</v>
       </c>
       <c r="R51" t="n">
-        <v>7140946</v>
+        <v>7140999</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6608,7 +6569,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6618,7 +6579,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6644,13 +6605,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266486</t>
+          <t>https://artportalen.se/Sighting/126266051</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126266654</v>
+        <v>126266106</v>
       </c>
       <c r="B52" t="n">
         <v>99035</v>
@@ -6680,7 +6641,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6688,16 +6649,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>470901</v>
+        <v>470925</v>
       </c>
       <c r="R52" t="n">
-        <v>7140921</v>
+        <v>7141000</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6729,7 +6695,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6739,7 +6705,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6765,13 +6731,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266654</t>
+          <t>https://artportalen.se/Sighting/126266106</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126266987</v>
+        <v>126266189</v>
       </c>
       <c r="B53" t="n">
         <v>99035</v>
@@ -6801,7 +6767,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6820,10 +6786,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>470927</v>
+        <v>470917</v>
       </c>
       <c r="R53" t="n">
-        <v>7140793</v>
+        <v>7140990</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6855,7 +6821,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6865,7 +6831,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6891,13 +6857,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266987</t>
+          <t>https://artportalen.se/Sighting/126266189</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126267316</v>
+        <v>126266486</v>
       </c>
       <c r="B54" t="n">
         <v>99035</v>
@@ -6927,7 +6893,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6935,24 +6901,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471000</v>
+        <v>470908</v>
       </c>
       <c r="R54" t="n">
-        <v>7140801</v>
+        <v>7140946</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6981,7 +6942,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6991,7 +6952,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7017,13 +6978,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126267316</t>
+          <t>https://artportalen.se/Sighting/126266486</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126782391</v>
+        <v>126266654</v>
       </c>
       <c r="B55" t="n">
         <v>99035</v>
@@ -7053,7 +7014,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7061,21 +7022,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470927</v>
+        <v>470901</v>
       </c>
       <c r="R55" t="n">
-        <v>7140809</v>
+        <v>7140921</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7102,22 +7058,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7143,16 +7099,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782391</t>
+          <t>https://artportalen.se/Sighting/126266654</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126266225</v>
+        <v>126266987</v>
       </c>
       <c r="B56" t="n">
-        <v>99022</v>
+        <v>99035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7160,26 +7116,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7189,7 +7145,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7198,10 +7154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470925</v>
+        <v>470927</v>
       </c>
       <c r="R56" t="n">
-        <v>7141000</v>
+        <v>7140793</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7233,7 +7189,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7243,7 +7199,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7269,48 +7225,48 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266225</t>
+          <t>https://artportalen.se/Sighting/126266987</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118608782</v>
+        <v>126267316</v>
       </c>
       <c r="B57" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7320,14 +7276,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471181</v>
+        <v>471000</v>
       </c>
       <c r="R57" t="n">
-        <v>7140954</v>
+        <v>7140801</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7354,12 +7310,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7385,43 +7351,43 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608782</t>
+          <t>https://artportalen.se/Sighting/126267316</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118609933</v>
+        <v>126782391</v>
       </c>
       <c r="B58" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7431,19 +7397,19 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>471229</v>
+        <v>470927</v>
       </c>
       <c r="R58" t="n">
-        <v>7140929</v>
+        <v>7140809</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7470,12 +7436,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7486,11 +7462,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7506,68 +7477,54 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118609933</t>
+          <t>https://artportalen.se/Sighting/126782391</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118610401</v>
+        <v>136195691</v>
       </c>
       <c r="B59" t="n">
-        <v>99118</v>
+        <v>99633</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>471080</v>
+        <v>470994</v>
       </c>
       <c r="R59" t="n">
-        <v>7140963</v>
+        <v>7141026</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7591,12 +7548,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7607,63 +7574,58 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610401</t>
+          <t>https://artportalen.se/Sighting/136195691</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118610548</v>
+        <v>126266225</v>
       </c>
       <c r="B60" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7673,19 +7635,19 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>471004</v>
+        <v>470925</v>
       </c>
       <c r="R60" t="n">
-        <v>7140974</v>
+        <v>7141000</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7712,12 +7674,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7728,11 +7700,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7748,13 +7715,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610548</t>
+          <t>https://artportalen.se/Sighting/126266225</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118610957</v>
+        <v>118608782</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7784,29 +7751,29 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471000</v>
+        <v>471181</v>
       </c>
       <c r="R61" t="n">
-        <v>7140801</v>
+        <v>7140954</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7864,13 +7831,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610957</t>
+          <t>https://artportalen.se/Sighting/118608782</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118611103</v>
+        <v>118609933</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7900,7 +7867,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7915,14 +7882,14 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470955</v>
+        <v>471229</v>
       </c>
       <c r="R62" t="n">
-        <v>7140903</v>
+        <v>7140929</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7966,6 +7933,11 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7980,13 +7952,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611103</t>
+          <t>https://artportalen.se/Sighting/118609933</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118613050</v>
+        <v>118610401</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -8016,7 +7988,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8026,19 +7998,19 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471123</v>
+        <v>471080</v>
       </c>
       <c r="R63" t="n">
-        <v>7140909</v>
+        <v>7140963</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -8082,6 +8054,11 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8096,13 +8073,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118613050</t>
+          <t>https://artportalen.se/Sighting/118610401</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118654949</v>
+        <v>118610548</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -8132,29 +8109,29 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471177</v>
+        <v>471004</v>
       </c>
       <c r="R64" t="n">
-        <v>7140901</v>
+        <v>7140974</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8181,12 +8158,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8197,6 +8174,11 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8212,13 +8194,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118654949</t>
+          <t>https://artportalen.se/Sighting/118610548</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118655215</v>
+        <v>118610957</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -8248,17 +8230,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8267,13 +8249,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471154</v>
+        <v>471000</v>
       </c>
       <c r="R65" t="n">
-        <v>7140912</v>
+        <v>7140801</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8297,12 +8279,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8328,13 +8310,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118655215</t>
+          <t>https://artportalen.se/Sighting/118610957</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118656206</v>
+        <v>118611103</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -8364,7 +8346,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8372,19 +8354,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471176</v>
+        <v>470955</v>
       </c>
       <c r="R66" t="n">
-        <v>7140877</v>
+        <v>7140903</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8408,22 +8395,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8449,13 +8426,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656206</t>
+          <t>https://artportalen.se/Sighting/118611103</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118656399</v>
+        <v>118613050</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -8485,12 +8462,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8504,13 +8481,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471159</v>
+        <v>471123</v>
       </c>
       <c r="R67" t="n">
-        <v>7140899</v>
+        <v>7140909</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8534,22 +8511,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8575,13 +8542,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656399</t>
+          <t>https://artportalen.se/Sighting/118613050</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118656619</v>
+        <v>118654949</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -8611,7 +8578,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8630,13 +8597,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471105</v>
+        <v>471177</v>
       </c>
       <c r="R68" t="n">
-        <v>7140950</v>
+        <v>7140901</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8663,19 +8630,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8701,13 +8658,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656619</t>
+          <t>https://artportalen.se/Sighting/118654949</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118657575</v>
+        <v>118655215</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -8737,12 +8694,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8756,13 +8713,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470892</v>
+        <v>471154</v>
       </c>
       <c r="R69" t="n">
-        <v>7140851</v>
+        <v>7140912</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8789,19 +8746,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8827,13 +8774,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118657575</t>
+          <t>https://artportalen.se/Sighting/118655215</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118658516</v>
+        <v>118656206</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8863,17 +8810,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8882,10 +8824,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471011</v>
+        <v>471176</v>
       </c>
       <c r="R70" t="n">
-        <v>7140807</v>
+        <v>7140877</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8917,7 +8859,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8927,12 +8869,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8958,16 +8895,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118658516</t>
+          <t>https://artportalen.se/Sighting/118656206</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136196782</v>
+        <v>118656399</v>
       </c>
       <c r="B71" t="n">
-        <v>99294</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8992,22 +8929,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471038</v>
+        <v>471159</v>
       </c>
       <c r="R71" t="n">
-        <v>7140811</v>
+        <v>7140899</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9034,22 +8980,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9064,59 +9010,59 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136196782</t>
+          <t>https://artportalen.se/Sighting/118656399</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126264186</v>
+        <v>118656619</v>
       </c>
       <c r="B72" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -9130,13 +9076,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470971</v>
+        <v>471105</v>
       </c>
       <c r="R72" t="n">
-        <v>7140842</v>
+        <v>7140950</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9160,22 +9106,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9201,48 +9147,48 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126264186</t>
+          <t>https://artportalen.se/Sighting/118656619</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126264597</v>
+        <v>118657575</v>
       </c>
       <c r="B73" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -9256,10 +9202,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470938</v>
+        <v>470892</v>
       </c>
       <c r="R73" t="n">
-        <v>7141021</v>
+        <v>7140851</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -9286,22 +9232,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9327,53 +9273,53 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126264597</t>
+          <t>https://artportalen.se/Sighting/118657575</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126266135</v>
+        <v>118658516</v>
       </c>
       <c r="B74" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9382,13 +9328,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>470925</v>
+        <v>471011</v>
       </c>
       <c r="R74" t="n">
-        <v>7141000</v>
+        <v>7140807</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9412,22 +9358,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9453,65 +9404,56 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266135</t>
+          <t>https://artportalen.se/Sighting/118658516</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126273173</v>
+        <v>136196782</v>
       </c>
       <c r="B75" t="n">
-        <v>99140</v>
+        <v>99295</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>470992</v>
+        <v>471038</v>
       </c>
       <c r="R75" t="n">
-        <v>7140849</v>
+        <v>7140811</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9538,12 +9480,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9558,24 +9510,24 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126273173</t>
+          <t>https://artportalen.se/Sighting/136196782</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126781777</v>
+        <v>126264186</v>
       </c>
       <c r="B76" t="n">
         <v>99140</v>
@@ -9603,20 +9555,34 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>470980</v>
+        <v>470971</v>
       </c>
       <c r="R76" t="n">
-        <v>7140865</v>
+        <v>7140842</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9640,22 +9606,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9681,13 +9647,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126781777</t>
+          <t>https://artportalen.se/Sighting/126264186</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126782585</v>
+        <v>126264597</v>
       </c>
       <c r="B77" t="n">
         <v>99140</v>
@@ -9717,7 +9683,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9727,7 +9693,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9736,10 +9702,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>470849</v>
+        <v>470938</v>
       </c>
       <c r="R77" t="n">
-        <v>7140849</v>
+        <v>7141021</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -9766,22 +9732,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9807,49 +9773,68 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782585</t>
+          <t>https://artportalen.se/Sighting/126264597</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136202502</v>
+        <v>126266135</v>
       </c>
       <c r="B78" t="n">
-        <v>93386</v>
+        <v>99140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6331649</v>
+        <v>221952</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon dititomentosus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Svantesson</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471081</v>
+        <v>470925</v>
       </c>
       <c r="R78" t="n">
-        <v>7140813</v>
+        <v>7141000</v>
       </c>
       <c r="S78" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9873,12 +9858,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9887,32 +9882,483 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266135</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126273173</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>470992</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7140849</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126273173</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126781777</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>470980</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7140865</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126781777</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126782585</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>470849</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7140849</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126782585</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>136202502</v>
+      </c>
+      <c r="B82" t="n">
+        <v>93387</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6331649</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Phellodon dititomentosus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Svantesson</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>471081</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7140813</v>
+      </c>
+      <c r="S82" t="n">
+        <v>71</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
           <t>Björn Larsson</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn, Irena Koelemeijer</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
         <is>
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
+      <c r="AZ82" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136202502</t>
         </is>
@@ -9997,6 +10443,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ82"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1239,51 +1239,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136195675</v>
+        <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>91598</v>
+        <v>92782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470996</v>
+        <v>471009</v>
       </c>
       <c r="R7" t="n">
-        <v>7141053</v>
+        <v>7140893</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,22 +1304,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,7 +1328,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1349,16 +1345,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136195675</t>
+          <t>https://artportalen.se/Sighting/136246185</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136195674</v>
+        <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>91598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,37 +1362,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>900</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470994</v>
+        <v>470996</v>
       </c>
       <c r="R8" t="n">
-        <v>7140815</v>
+        <v>7141053</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,6 +1443,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1461,54 +1461,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136195674</t>
+          <t>https://artportalen.se/Sighting/136195675</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118649741</v>
+        <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>91920</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471038</v>
+        <v>470994</v>
       </c>
       <c r="R9" t="n">
-        <v>7140797</v>
+        <v>7140815</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,22 +1532,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,47 +1562,51 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118649741</t>
+          <t>https://artportalen.se/Sighting/136195674</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136202511</v>
+        <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>87549</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3624</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1610,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471019</v>
+        <v>471009</v>
       </c>
       <c r="R10" t="n">
-        <v>7141064</v>
+        <v>7140893</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,12 +1644,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,40 +1670,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202511</t>
+          <t>https://artportalen.se/Sighting/136246184</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136202482</v>
+        <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>87512</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,21 +1702,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3739</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1721,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471029</v>
+        <v>471224</v>
       </c>
       <c r="R11" t="n">
-        <v>7141075</v>
+        <v>7140994</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1751,12 +1756,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,57 +1783,52 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202482</t>
+          <t>https://artportalen.se/Sighting/136246189</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136202509</v>
+        <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>87512</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3739</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,13 +1838,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471019</v>
+        <v>470968</v>
       </c>
       <c r="R12" t="n">
-        <v>7141064</v>
+        <v>7140873</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1858,12 +1868,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,78 +1894,69 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202509</t>
+          <t>https://artportalen.se/Sighting/136246183</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136202506</v>
+        <v>118649741</v>
       </c>
       <c r="B13" t="n">
-        <v>89278</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4404</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sotvaxskivling</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus camarophyllus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471081</v>
+        <v>471038</v>
       </c>
       <c r="R13" t="n">
-        <v>7140813</v>
+        <v>7140797</v>
       </c>
       <c r="S13" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,12 +1980,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,78 +2006,69 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202506</t>
+          <t>https://artportalen.se/Sighting/118649741</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128051879</v>
+        <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>89156</v>
+        <v>92416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4412</v>
+        <v>2064</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470929</v>
+        <v>471234</v>
       </c>
       <c r="R14" t="n">
-        <v>7141002</v>
+        <v>7140957</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2080,12 +2092,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,33 +2116,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Staaf, Rashid Kadhim</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128051879</t>
+          <t>https://artportalen.se/Sighting/136246188</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136200761</v>
+        <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>92029</v>
+        <v>87549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,40 +2151,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>3624</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470985</v>
+        <v>471019</v>
       </c>
       <c r="R15" t="n">
-        <v>7141033</v>
+        <v>7141064</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,34 +2215,42 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200761</t>
+          <t>https://artportalen.se/Sighting/136202511</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118615387</v>
+        <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>87512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,37 +2258,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>3739</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471126</v>
+        <v>471029</v>
       </c>
       <c r="R16" t="n">
-        <v>7140737</v>
+        <v>7141075</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,12 +2312,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,83 +2329,73 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
+      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118615387</t>
+          <t>https://artportalen.se/Sighting/136202482</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118653585</v>
+        <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>80467</v>
+        <v>87512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>3739</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471126</v>
+        <v>471019</v>
       </c>
       <c r="R17" t="n">
-        <v>7140737</v>
+        <v>7141064</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2405,22 +2419,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,69 +2435,78 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118653585</t>
+          <t>https://artportalen.se/Sighting/136202509</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115383522</v>
+        <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>89278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>4404</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471015</v>
+        <v>471081</v>
       </c>
       <c r="R18" t="n">
-        <v>7141073</v>
+        <v>7140813</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2517,17 +2530,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Även observerat Spillkråka flygande flera ggr i veckan.</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,75 +2547,74 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115383522</t>
+          <t>https://artportalen.se/Sighting/136202506</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118652300</v>
+        <v>128051879</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>89156</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470932</v>
+        <v>470929</v>
       </c>
       <c r="R19" t="n">
-        <v>7140929</v>
+        <v>7141002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2634,22 +2641,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,27 +2661,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Johan Staaf, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118652300</t>
+          <t>https://artportalen.se/Sighting/128051879</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118652356</v>
+        <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>92029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2692,42 +2689,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471011</v>
+        <v>470985</v>
       </c>
       <c r="R20" t="n">
-        <v>7140906</v>
+        <v>7141033</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,22 +2746,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,76 +2760,72 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118652356</t>
+          <t>https://artportalen.se/Sighting/136200761</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118654317</v>
+        <v>118615387</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471203</v>
+        <v>471126</v>
       </c>
       <c r="R21" t="n">
-        <v>7140769</v>
+        <v>7140737</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2868,27 +2849,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Födosök Spillkråka</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,6 +2865,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2914,16 +2895,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118654317</t>
+          <t>https://artportalen.se/Sighting/118615387</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118656092</v>
+        <v>118653585</v>
       </c>
       <c r="B22" t="n">
-        <v>57950</v>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,42 +2912,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471143</v>
+        <v>471126</v>
       </c>
       <c r="R22" t="n">
-        <v>7141012</v>
+        <v>7140737</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,22 +2966,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,13 +3007,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656092</t>
+          <t>https://artportalen.se/Sighting/118653585</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123377834</v>
+        <v>115383522</v>
       </c>
       <c r="B23" t="n">
         <v>57950</v>
@@ -3066,21 +3042,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471007</v>
+        <v>471015</v>
       </c>
       <c r="R23" t="n">
-        <v>7141045</v>
+        <v>7141073</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3107,17 +3078,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Tydliga färska födosök spillkråka</t>
+          <t>Även observerat Spillkråka flygande flera ggr i veckan.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,28 +3099,33 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377834</t>
+          <t>https://artportalen.se/Sighting/115383522</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126264916</v>
+        <v>118652300</v>
       </c>
       <c r="B24" t="n">
         <v>57950</v>
@@ -3180,7 +3156,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3189,13 +3165,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470985</v>
+        <v>470932</v>
       </c>
       <c r="R24" t="n">
-        <v>7141047</v>
+        <v>7140929</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3219,22 +3195,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,13 +3236,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126264916</t>
+          <t>https://artportalen.se/Sighting/118652300</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128157802</v>
+        <v>118652356</v>
       </c>
       <c r="B25" t="n">
         <v>57950</v>
@@ -3297,22 +3273,22 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471213</v>
+        <v>471011</v>
       </c>
       <c r="R25" t="n">
-        <v>7140791</v>
+        <v>7140906</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3336,22 +3312,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,33 +3353,33 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128157802</t>
+          <t>https://artportalen.se/Sighting/118652356</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111954389</v>
+        <v>118654317</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3412,31 +3388,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471015</v>
+        <v>471203</v>
       </c>
       <c r="R26" t="n">
-        <v>7141073</v>
+        <v>7140769</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,12 +3429,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosök Spillkråka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,44 +3464,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jennie Ramsell</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111954389</t>
+          <t>https://artportalen.se/Sighting/118654317</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118745232</v>
+        <v>118656092</v>
       </c>
       <c r="B27" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3526,19 +3510,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>470948</v>
+        <v>471143</v>
       </c>
       <c r="R27" t="n">
-        <v>7141024</v>
+        <v>7141012</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3562,12 +3551,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3593,33 +3592,33 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118745232</t>
+          <t>https://artportalen.se/Sighting/118656092</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122603006</v>
+        <v>123377834</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3628,29 +3627,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>470980</v>
+        <v>471007</v>
       </c>
       <c r="R28" t="n">
-        <v>7140865</v>
+        <v>7141045</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3674,17 +3668,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
+          <t>Tydliga färska födosök spillkråka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3695,11 +3689,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3715,33 +3704,33 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122603006</t>
+          <t>https://artportalen.se/Sighting/123377834</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123377064</v>
+        <v>126264916</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3750,16 +3739,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471175</v>
+        <v>470985</v>
       </c>
       <c r="R29" t="n">
-        <v>7140991</v>
+        <v>7141047</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3786,17 +3780,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,33 +3821,33 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377064</t>
+          <t>https://artportalen.se/Sighting/126264916</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123377276</v>
+        <v>128157802</v>
       </c>
       <c r="B30" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3856,26 +3855,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471094</v>
+        <v>471213</v>
       </c>
       <c r="R30" t="n">
-        <v>7141017</v>
+        <v>7140791</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3902,17 +3897,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Helt färska ringhack på gran. Se bilder.</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,13 +3938,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377276</t>
+          <t>https://artportalen.se/Sighting/128157802</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123377514</v>
+        <v>111954389</v>
       </c>
       <c r="B31" t="n">
         <v>57953</v>
@@ -3972,26 +3972,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Leden upp till Kalberget, Håkafot, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471066</v>
+        <v>471015</v>
       </c>
       <c r="R31" t="n">
-        <v>7141025</v>
+        <v>7141073</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4018,17 +4021,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4043,24 +4041,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Jennie Ramsell</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123377514</t>
+          <t>https://artportalen.se/Sighting/111954389</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126782340</v>
+        <v>118745232</v>
       </c>
       <c r="B32" t="n">
         <v>57953</v>
@@ -4089,24 +4087,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>470941</v>
+        <v>470948</v>
       </c>
       <c r="R32" t="n">
-        <v>7140824</v>
+        <v>7141024</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4130,22 +4123,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,13 +4154,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782340</t>
+          <t>https://artportalen.se/Sighting/118745232</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126783407</v>
+        <v>122603006</v>
       </c>
       <c r="B33" t="n">
         <v>57953</v>
@@ -4206,9 +4189,14 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4217,13 +4205,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471028</v>
+        <v>470980</v>
       </c>
       <c r="R33" t="n">
-        <v>7140823</v>
+        <v>7140865</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4247,27 +4235,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
+          <t>Färska ringhackni stor mängd som tillkommit senaste veckan.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,6 +4256,11 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4293,13 +4276,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126783407</t>
+          <t>https://artportalen.se/Sighting/122603006</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126785249</v>
+        <v>123377064</v>
       </c>
       <c r="B34" t="n">
         <v>57953</v>
@@ -4327,26 +4310,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470934</v>
+        <v>471175</v>
       </c>
       <c r="R34" t="n">
-        <v>7140818</v>
+        <v>7140991</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4373,27 +4347,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4419,33 +4383,33 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126785249</t>
+          <t>https://artportalen.se/Sighting/123377064</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118619895</v>
+        <v>123377276</v>
       </c>
       <c r="B35" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4453,35 +4417,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471080</v>
+        <v>471094</v>
       </c>
       <c r="R35" t="n">
-        <v>7140901</v>
+        <v>7141017</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4505,22 +4463,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Helt färska ringhack på gran. Se bilder.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4531,11 +4484,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4551,33 +4499,33 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118619895</t>
+          <t>https://artportalen.se/Sighting/123377276</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118632946</v>
+        <v>123377514</v>
       </c>
       <c r="B36" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4587,29 +4535,24 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>ägg</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471124</v>
+        <v>471066</v>
       </c>
       <c r="R36" t="n">
-        <v>7140767</v>
+        <v>7141025</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4636,27 +4579,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
+          <t>Helt gärska ringhack från Tretå. Se bilder.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,33 +4615,33 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118632946</t>
+          <t>https://artportalen.se/Sighting/123377514</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118633149</v>
+        <v>126782340</v>
       </c>
       <c r="B37" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4716,19 +4649,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4737,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471126</v>
+        <v>470941</v>
       </c>
       <c r="R37" t="n">
-        <v>7140737</v>
+        <v>7140824</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4767,22 +4691,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4808,33 +4732,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118633149</t>
+          <t>https://artportalen.se/Sighting/126782340</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118653001</v>
+        <v>126783407</v>
       </c>
       <c r="B38" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4842,19 +4766,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4863,13 +4778,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471105</v>
+        <v>471028</v>
       </c>
       <c r="R38" t="n">
-        <v>7140803</v>
+        <v>7140823</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4893,22 +4808,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Observerat födosökande tretå i närheten idag se andra rapporteringar i området.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4934,33 +4854,33 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118653001</t>
+          <t>https://artportalen.se/Sighting/126783407</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118655469</v>
+        <v>126785249</v>
       </c>
       <c r="B39" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4973,14 +4893,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äggskal</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4989,13 +4904,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471147</v>
+        <v>470934</v>
       </c>
       <c r="R39" t="n">
-        <v>7140935</v>
+        <v>7140818</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5019,27 +4934,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
+          <t>Födosökande tretå på elstolpe. Precis bredvid den rapporterade granen med färska ringhack och fösosök.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5065,13 +4980,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118655469</t>
+          <t>https://artportalen.se/Sighting/126785249</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118657198</v>
+        <v>118619895</v>
       </c>
       <c r="B40" t="n">
         <v>57132</v>
@@ -5112,7 +5027,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5121,10 +5036,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470996</v>
+        <v>471080</v>
       </c>
       <c r="R40" t="n">
-        <v>7140928</v>
+        <v>7140901</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5151,27 +5066,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Järpe med ungar boplats vid vindfällen</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5182,6 +5092,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5197,13 +5112,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118657198</t>
+          <t>https://artportalen.se/Sighting/118619895</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118658352</v>
+        <v>118632946</v>
       </c>
       <c r="B41" t="n">
         <v>57132</v>
@@ -5231,20 +5146,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5253,13 +5167,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471000</v>
+        <v>471124</v>
       </c>
       <c r="R41" t="n">
-        <v>7140830</v>
+        <v>7140767</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5283,22 +5197,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Observerade Järpe med ungar en bit ifrån boplatsen!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5324,13 +5243,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118658352</t>
+          <t>https://artportalen.se/Sighting/118632946</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118701309</v>
+        <v>118633149</v>
       </c>
       <c r="B42" t="n">
         <v>57132</v>
@@ -5358,17 +5277,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>bo, ägg/ungar</t>
@@ -5380,13 +5298,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471115</v>
+        <v>471126</v>
       </c>
       <c r="R42" t="n">
-        <v>7140993</v>
+        <v>7140737</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5410,17 +5328,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Järpehöna med minst 2 kycklingar befinner sig vid vindfälle av gran.</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5446,13 +5369,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118701309</t>
+          <t>https://artportalen.se/Sighting/118633149</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122603183</v>
+        <v>118653001</v>
       </c>
       <c r="B43" t="n">
         <v>57132</v>
@@ -5482,22 +5405,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5506,13 +5424,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471073</v>
+        <v>471105</v>
       </c>
       <c r="R43" t="n">
-        <v>7140813</v>
+        <v>7140803</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5536,17 +5454,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5557,11 +5480,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5577,13 +5495,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122603183</t>
+          <t>https://artportalen.se/Sighting/118653001</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126782059</v>
+        <v>118655469</v>
       </c>
       <c r="B44" t="n">
         <v>57132</v>
@@ -5618,17 +5536,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äggskal</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5637,13 +5550,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>470892</v>
+        <v>471147</v>
       </c>
       <c r="R44" t="n">
-        <v>7140851</v>
+        <v>7140935</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5667,27 +5580,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>Kläckt äggskal av Järpe i liten mossbeklädd nedsänkning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5713,13 +5626,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782059</t>
+          <t>https://artportalen.se/Sighting/118655469</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126782095</v>
+        <v>118657198</v>
       </c>
       <c r="B45" t="n">
         <v>57132</v>
@@ -5747,11 +5660,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>adult</t>
@@ -5764,7 +5673,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5773,13 +5682,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>470917</v>
+        <v>470996</v>
       </c>
       <c r="R45" t="n">
-        <v>7140839</v>
+        <v>7140928</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5803,27 +5712,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>Järpe med ungar boplats vid vindfällen</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5849,13 +5758,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782095</t>
+          <t>https://artportalen.se/Sighting/118657198</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126782120</v>
+        <v>118658352</v>
       </c>
       <c r="B46" t="n">
         <v>57132</v>
@@ -5883,11 +5792,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>adult</t>
@@ -5900,7 +5805,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5909,13 +5814,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>470941</v>
+        <v>471000</v>
       </c>
       <c r="R46" t="n">
-        <v>7140824</v>
+        <v>7140830</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5939,27 +5844,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5985,33 +5885,33 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782120</t>
+          <t>https://artportalen.se/Sighting/118658352</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118655326</v>
+        <v>118701309</v>
       </c>
       <c r="B47" t="n">
-        <v>58057</v>
+        <v>57132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6019,19 +5919,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6040,13 +5941,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471150</v>
+        <v>471115</v>
       </c>
       <c r="R47" t="n">
-        <v>7140890</v>
+        <v>7140993</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6070,22 +5971,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Järpehöna med minst 2 kycklingar befinner sig vid vindfälle av gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6111,16 +6007,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118655326</t>
+          <t>https://artportalen.se/Sighting/118701309</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118611615</v>
+        <v>122603183</v>
       </c>
       <c r="B48" t="n">
-        <v>99035</v>
+        <v>57132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6128,48 +6024,53 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>470931</v>
+        <v>471073</v>
       </c>
       <c r="R48" t="n">
-        <v>7140959</v>
+        <v>7140813</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6196,12 +6097,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Skrämd Järpehöna flyger upp ur skogsbrynet.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6212,6 +6118,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6227,16 +6138,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611615</t>
+          <t>https://artportalen.se/Sighting/122603183</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118654475</v>
+        <v>126782059</v>
       </c>
       <c r="B49" t="n">
-        <v>99035</v>
+        <v>57132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6244,36 +6155,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6282,13 +6198,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>471220</v>
+        <v>470892</v>
       </c>
       <c r="R49" t="n">
-        <v>7140873</v>
+        <v>7140851</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6312,22 +6228,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6353,16 +6274,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118654475</t>
+          <t>https://artportalen.se/Sighting/126782059</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118658808</v>
+        <v>126782095</v>
       </c>
       <c r="B50" t="n">
-        <v>99035</v>
+        <v>57132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6370,21 +6291,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6392,14 +6313,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6408,13 +6334,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>471124</v>
+        <v>470917</v>
       </c>
       <c r="R50" t="n">
-        <v>7140767</v>
+        <v>7140839</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6438,22 +6364,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6479,16 +6410,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118658808</t>
+          <t>https://artportalen.se/Sighting/126782095</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126266051</v>
+        <v>126782120</v>
       </c>
       <c r="B51" t="n">
-        <v>99035</v>
+        <v>57132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6496,36 +6427,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6534,13 +6470,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470969</v>
+        <v>470941</v>
       </c>
       <c r="R51" t="n">
-        <v>7140999</v>
+        <v>7140824</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6564,22 +6500,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Järpehona med 2 ungar. Råkar skrämma upp från riset precis vid leden upp mot Kalberget.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6605,53 +6546,53 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266051</t>
+          <t>https://artportalen.se/Sighting/126782120</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126266106</v>
+        <v>118655326</v>
       </c>
       <c r="B52" t="n">
-        <v>99035</v>
+        <v>58057</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6660,13 +6601,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>470925</v>
+        <v>471150</v>
       </c>
       <c r="R52" t="n">
-        <v>7141000</v>
+        <v>7140890</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6690,22 +6631,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6731,13 +6672,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266106</t>
+          <t>https://artportalen.se/Sighting/118655326</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126266189</v>
+        <v>118611615</v>
       </c>
       <c r="B53" t="n">
         <v>99035</v>
@@ -6767,7 +6708,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6777,19 +6718,19 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>470917</v>
+        <v>470931</v>
       </c>
       <c r="R53" t="n">
-        <v>7140990</v>
+        <v>7140959</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6816,22 +6757,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6857,13 +6788,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266189</t>
+          <t>https://artportalen.se/Sighting/118611615</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126266486</v>
+        <v>118654475</v>
       </c>
       <c r="B54" t="n">
         <v>99035</v>
@@ -6893,12 +6824,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6907,13 +6843,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>470908</v>
+        <v>471220</v>
       </c>
       <c r="R54" t="n">
-        <v>7140946</v>
+        <v>7140873</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6937,22 +6873,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6978,13 +6914,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266486</t>
+          <t>https://artportalen.se/Sighting/118654475</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126266654</v>
+        <v>118658808</v>
       </c>
       <c r="B55" t="n">
         <v>99035</v>
@@ -7014,12 +6950,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7028,10 +6969,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470901</v>
+        <v>471124</v>
       </c>
       <c r="R55" t="n">
-        <v>7140921</v>
+        <v>7140767</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7058,22 +6999,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7099,13 +7040,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266654</t>
+          <t>https://artportalen.se/Sighting/118658808</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126266987</v>
+        <v>126266051</v>
       </c>
       <c r="B56" t="n">
         <v>99035</v>
@@ -7135,7 +7076,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7154,10 +7095,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470927</v>
+        <v>470969</v>
       </c>
       <c r="R56" t="n">
-        <v>7140793</v>
+        <v>7140999</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7189,7 +7130,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7199,7 +7140,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7225,13 +7166,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266987</t>
+          <t>https://artportalen.se/Sighting/126266051</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126267316</v>
+        <v>126266106</v>
       </c>
       <c r="B57" t="n">
         <v>99035</v>
@@ -7261,7 +7202,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7271,7 +7212,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7280,10 +7221,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471000</v>
+        <v>470925</v>
       </c>
       <c r="R57" t="n">
-        <v>7140801</v>
+        <v>7141000</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7315,7 +7256,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7325,7 +7266,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7351,13 +7292,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126267316</t>
+          <t>https://artportalen.se/Sighting/126266106</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126782391</v>
+        <v>126266189</v>
       </c>
       <c r="B58" t="n">
         <v>99035</v>
@@ -7387,7 +7328,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7397,7 +7338,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7406,10 +7347,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470927</v>
+        <v>470917</v>
       </c>
       <c r="R58" t="n">
-        <v>7140809</v>
+        <v>7140990</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7436,22 +7377,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7477,16 +7418,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782391</t>
+          <t>https://artportalen.se/Sighting/126266189</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136195691</v>
+        <v>126266486</v>
       </c>
       <c r="B59" t="n">
-        <v>99633</v>
+        <v>99035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7494,37 +7435,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>470994</v>
+        <v>470908</v>
       </c>
       <c r="R59" t="n">
-        <v>7141026</v>
+        <v>7140946</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7548,22 +7498,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7578,27 +7528,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136195691</t>
+          <t>https://artportalen.se/Sighting/126266486</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126266225</v>
+        <v>126266654</v>
       </c>
       <c r="B60" t="n">
-        <v>99022</v>
+        <v>99035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7606,26 +7556,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7633,21 +7583,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>470925</v>
+        <v>470901</v>
       </c>
       <c r="R60" t="n">
-        <v>7141000</v>
+        <v>7140921</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7679,7 +7624,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7689,7 +7634,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7715,65 +7660,65 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266225</t>
+          <t>https://artportalen.se/Sighting/126266654</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118608782</v>
+        <v>126266987</v>
       </c>
       <c r="B61" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471181</v>
+        <v>470927</v>
       </c>
       <c r="R61" t="n">
-        <v>7140954</v>
+        <v>7140793</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7800,12 +7745,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7831,43 +7786,43 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608782</t>
+          <t>https://artportalen.se/Sighting/126266987</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118609933</v>
+        <v>126267316</v>
       </c>
       <c r="B62" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7877,19 +7832,19 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Håagkat, Håagkat, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471229</v>
+        <v>471000</v>
       </c>
       <c r="R62" t="n">
-        <v>7140929</v>
+        <v>7140801</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7916,12 +7871,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7932,11 +7897,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7952,43 +7912,43 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118609933</t>
+          <t>https://artportalen.se/Sighting/126267316</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118610401</v>
+        <v>126782391</v>
       </c>
       <c r="B63" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7998,19 +7958,19 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471080</v>
+        <v>470927</v>
       </c>
       <c r="R63" t="n">
-        <v>7140963</v>
+        <v>7140809</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -8037,12 +7997,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8053,11 +8023,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8073,68 +8038,54 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610401</t>
+          <t>https://artportalen.se/Sighting/126782391</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118610548</v>
+        <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99118</v>
+        <v>99633</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471004</v>
+        <v>470994</v>
       </c>
       <c r="R64" t="n">
-        <v>7140974</v>
+        <v>7141026</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8158,12 +8109,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8174,63 +8135,58 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610548</t>
+          <t>https://artportalen.se/Sighting/136195691</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118610957</v>
+        <v>126266225</v>
       </c>
       <c r="B65" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8240,7 +8196,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8249,10 +8205,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471000</v>
+        <v>470925</v>
       </c>
       <c r="R65" t="n">
-        <v>7140801</v>
+        <v>7141000</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8279,12 +8235,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8310,13 +8276,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118610957</t>
+          <t>https://artportalen.se/Sighting/126266225</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118611103</v>
+        <v>118608782</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -8346,29 +8312,29 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Håkafot, Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470955</v>
+        <v>471181</v>
       </c>
       <c r="R66" t="n">
-        <v>7140903</v>
+        <v>7140954</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8426,13 +8392,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118611103</t>
+          <t>https://artportalen.se/Sighting/118608782</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118613050</v>
+        <v>118609933</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -8462,7 +8428,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8472,19 +8438,19 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håagkat, Håagkat, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471123</v>
+        <v>471229</v>
       </c>
       <c r="R67" t="n">
-        <v>7140909</v>
+        <v>7140929</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8528,6 +8494,11 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
@@ -8542,13 +8513,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118613050</t>
+          <t>https://artportalen.se/Sighting/118609933</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118654949</v>
+        <v>118610401</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -8578,29 +8549,29 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471177</v>
+        <v>471080</v>
       </c>
       <c r="R68" t="n">
-        <v>7140901</v>
+        <v>7140963</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8627,12 +8598,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8643,6 +8614,11 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8658,13 +8634,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118654949</t>
+          <t>https://artportalen.se/Sighting/118610401</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118655215</v>
+        <v>118610548</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -8694,32 +8670,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471154</v>
+        <v>471004</v>
       </c>
       <c r="R69" t="n">
-        <v>7140912</v>
+        <v>7140974</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8743,12 +8719,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8759,6 +8735,11 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8774,13 +8755,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118655215</t>
+          <t>https://artportalen.se/Sighting/118610548</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118656206</v>
+        <v>118610957</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8810,7 +8791,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8818,19 +8799,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471176</v>
+        <v>471000</v>
       </c>
       <c r="R70" t="n">
-        <v>7140877</v>
+        <v>7140801</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8854,22 +8840,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8895,13 +8871,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656206</t>
+          <t>https://artportalen.se/Sighting/118610957</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118656399</v>
+        <v>118611103</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8931,32 +8907,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Håkafot, Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471159</v>
+        <v>470955</v>
       </c>
       <c r="R71" t="n">
-        <v>7140899</v>
+        <v>7140903</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8980,22 +8956,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9021,13 +8987,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656399</t>
+          <t>https://artportalen.se/Sighting/118611103</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118656619</v>
+        <v>118613050</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -9057,12 +9023,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -9076,13 +9042,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471105</v>
+        <v>471123</v>
       </c>
       <c r="R72" t="n">
-        <v>7140950</v>
+        <v>7140909</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9106,22 +9072,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9147,13 +9103,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118656619</t>
+          <t>https://artportalen.se/Sighting/118613050</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118657575</v>
+        <v>118654949</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -9183,7 +9139,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9202,10 +9158,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470892</v>
+        <v>471177</v>
       </c>
       <c r="R73" t="n">
-        <v>7140851</v>
+        <v>7140901</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -9235,19 +9191,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9273,13 +9219,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118657575</t>
+          <t>https://artportalen.se/Sighting/118654949</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118658516</v>
+        <v>118655215</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -9309,7 +9255,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9319,7 +9265,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9328,13 +9274,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471011</v>
+        <v>471154</v>
       </c>
       <c r="R74" t="n">
-        <v>7140807</v>
+        <v>7140912</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9361,24 +9307,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9404,16 +9335,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118658516</t>
+          <t>https://artportalen.se/Sighting/118655215</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136196782</v>
+        <v>118656206</v>
       </c>
       <c r="B75" t="n">
-        <v>99295</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9438,7 +9369,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -9446,17 +9381,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471038</v>
+        <v>471176</v>
       </c>
       <c r="R75" t="n">
-        <v>7140811</v>
+        <v>7140877</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9480,22 +9415,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9510,59 +9445,59 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136196782</t>
+          <t>https://artportalen.se/Sighting/118656206</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126264186</v>
+        <v>118656399</v>
       </c>
       <c r="B76" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9576,13 +9511,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>470971</v>
+        <v>471159</v>
       </c>
       <c r="R76" t="n">
-        <v>7140842</v>
+        <v>7140899</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9606,22 +9541,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9647,48 +9582,48 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126264186</t>
+          <t>https://artportalen.se/Sighting/118656399</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126264597</v>
+        <v>118656619</v>
       </c>
       <c r="B77" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9702,13 +9637,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>470938</v>
+        <v>471105</v>
       </c>
       <c r="R77" t="n">
-        <v>7141021</v>
+        <v>7140950</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9732,22 +9667,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9773,48 +9708,48 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126264597</t>
+          <t>https://artportalen.se/Sighting/118656619</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126266135</v>
+        <v>118657575</v>
       </c>
       <c r="B78" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9828,10 +9763,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470925</v>
+        <v>470892</v>
       </c>
       <c r="R78" t="n">
-        <v>7141000</v>
+        <v>7140851</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -9858,22 +9793,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9899,53 +9834,53 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126266135</t>
+          <t>https://artportalen.se/Sighting/118657575</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126273173</v>
+        <v>118658516</v>
       </c>
       <c r="B79" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9954,13 +9889,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470992</v>
+        <v>471011</v>
       </c>
       <c r="R79" t="n">
-        <v>7140849</v>
+        <v>7140807</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9984,12 +9919,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Va 2 kvm med mattbildnde rosetter samt ett 15-tal stängler i blomning.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10015,51 +9965,56 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126273173</t>
+          <t>https://artportalen.se/Sighting/118658516</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126781777</v>
+        <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99140</v>
+        <v>99295</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Håkafot, Jmt</t>
+          <t>Kalberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>470980</v>
+        <v>471038</v>
       </c>
       <c r="R80" t="n">
-        <v>7140865</v>
+        <v>7140811</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10086,22 +10041,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10116,24 +10071,24 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126781777</t>
+          <t>https://artportalen.se/Sighting/136196782</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126782585</v>
+        <v>126264186</v>
       </c>
       <c r="B81" t="n">
         <v>99140</v>
@@ -10163,7 +10118,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10173,7 +10128,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10182,10 +10137,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>470849</v>
+        <v>470971</v>
       </c>
       <c r="R81" t="n">
-        <v>7140849</v>
+        <v>7140842</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -10212,22 +10167,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10253,49 +10208,68 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126782585</t>
+          <t>https://artportalen.se/Sighting/126264186</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136202502</v>
+        <v>126264597</v>
       </c>
       <c r="B82" t="n">
-        <v>93387</v>
+        <v>99140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6331649</v>
+        <v>221952</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon dititomentosus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Svantesson</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kalberget, Jmt</t>
+          <t>Håkafot, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471081</v>
+        <v>470938</v>
       </c>
       <c r="R82" t="n">
-        <v>7140813</v>
+        <v>7141021</v>
       </c>
       <c r="S82" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10319,12 +10293,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10333,32 +10317,609 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126264597</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126266135</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>470925</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7141000</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266135</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126273173</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>470992</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7140849</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126273173</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126781777</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>470980</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7140865</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126781777</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126782585</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Håkafot, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>470849</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7140849</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126782585</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>136202502</v>
+      </c>
+      <c r="B87" t="n">
+        <v>93387</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6331649</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Phellodon dititomentosus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Svantesson</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>471081</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7140813</v>
+      </c>
+      <c r="S87" t="n">
+        <v>71</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
           <t>Björn Larsson</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
+      <c r="AX87" t="inlineStr">
         <is>
           <t>Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn, Irena Koelemeijer</t>
         </is>
       </c>
-      <c r="AY82" t="inlineStr">
+      <c r="AY87" t="inlineStr">
         <is>
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
+      <c r="AZ87" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136202502</t>
         </is>
@@ -10447,6 +11008,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92416</v>
+        <v>92417</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87549</v>
+        <v>87550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+          <t>Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
+          <t>Johan Råghall, Karl Soler Kinnerbäck, Linnea Ingelsbo, Maja Östlund, Margaux Boeraeve, Martin Peraic, Noel Wieser, Rashid Kadhim, Simon Rung, Sten Svantesson, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89278</v>
+        <v>89279</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93387</v>
+        <v>93388</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92783</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92417</v>
+        <v>92423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87550</v>
+        <v>87556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87513</v>
+        <v>87519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87513</v>
+        <v>87519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89279</v>
+        <v>89285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93388</v>
+        <v>93394</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92423</v>
+        <v>92424</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87556</v>
+        <v>87557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87519</v>
+        <v>87520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87519</v>
+        <v>87520</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89285</v>
+        <v>89286</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93394</v>
+        <v>93395</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10832,6 +10832,11 @@
       </c>
       <c r="E87" t="n">
         <v>6331649</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Huldretaggsvamp</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92790</v>
+        <v>92796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91606</v>
+        <v>91612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92424</v>
+        <v>92430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87557</v>
+        <v>87563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87520</v>
+        <v>87526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87520</v>
+        <v>87526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89286</v>
+        <v>89292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93395</v>
+        <v>93401</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92796</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91612</v>
+        <v>91619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92430</v>
+        <v>92437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87563</v>
+        <v>87570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87526</v>
+        <v>87533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87526</v>
+        <v>87533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89292</v>
+        <v>89299</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93401</v>
+        <v>93408</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92803</v>
+        <v>92804</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91619</v>
+        <v>91620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92437</v>
+        <v>92438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89299</v>
+        <v>89300</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92804</v>
+        <v>92817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91620</v>
+        <v>91633</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92438</v>
+        <v>92451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87533</v>
+        <v>87546</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87533</v>
+        <v>87546</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89300</v>
+        <v>89313</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93409</v>
+        <v>93422</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92817</v>
+        <v>92818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91633</v>
+        <v>91634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92451</v>
+        <v>92452</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87583</v>
+        <v>87584</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87546</v>
+        <v>87547</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87546</v>
+        <v>87547</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89313</v>
+        <v>89314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93422</v>
+        <v>93423</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
